--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H727"/>
+  <dimension ref="A1:H749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20801,6 +20801,622 @@
         <v>0</v>
       </c>
       <c r="H727" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>0</v>
+      </c>
+      <c r="D728" t="n">
+        <v>0</v>
+      </c>
+      <c r="E728" t="n">
+        <v>0</v>
+      </c>
+      <c r="F728" t="n">
+        <v>0</v>
+      </c>
+      <c r="G728" t="n">
+        <v>0</v>
+      </c>
+      <c r="H728" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>0</v>
+      </c>
+      <c r="D729" t="n">
+        <v>0</v>
+      </c>
+      <c r="E729" t="n">
+        <v>0</v>
+      </c>
+      <c r="F729" t="n">
+        <v>0</v>
+      </c>
+      <c r="G729" t="n">
+        <v>0</v>
+      </c>
+      <c r="H729" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D730" t="n">
+        <v>0</v>
+      </c>
+      <c r="E730" t="n">
+        <v>0</v>
+      </c>
+      <c r="F730" t="n">
+        <v>0</v>
+      </c>
+      <c r="G730" t="n">
+        <v>0</v>
+      </c>
+      <c r="H730" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>86539.92200000001</v>
+      </c>
+      <c r="D731" t="n">
+        <v>0</v>
+      </c>
+      <c r="E731" t="n">
+        <v>0</v>
+      </c>
+      <c r="F731" t="n">
+        <v>0</v>
+      </c>
+      <c r="G731" t="n">
+        <v>0</v>
+      </c>
+      <c r="H731" t="n">
+        <v>86539.92200000001</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D732" t="n">
+        <v>0</v>
+      </c>
+      <c r="E732" t="n">
+        <v>0</v>
+      </c>
+      <c r="F732" t="n">
+        <v>0</v>
+      </c>
+      <c r="G732" t="n">
+        <v>0</v>
+      </c>
+      <c r="H732" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>0</v>
+      </c>
+      <c r="D733" t="n">
+        <v>0</v>
+      </c>
+      <c r="E733" t="n">
+        <v>0</v>
+      </c>
+      <c r="F733" t="n">
+        <v>0</v>
+      </c>
+      <c r="G733" t="n">
+        <v>0</v>
+      </c>
+      <c r="H733" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D734" t="n">
+        <v>0</v>
+      </c>
+      <c r="E734" t="n">
+        <v>0</v>
+      </c>
+      <c r="F734" t="n">
+        <v>0</v>
+      </c>
+      <c r="G734" t="n">
+        <v>0</v>
+      </c>
+      <c r="H734" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D735" t="n">
+        <v>0</v>
+      </c>
+      <c r="E735" t="n">
+        <v>0</v>
+      </c>
+      <c r="F735" t="n">
+        <v>0</v>
+      </c>
+      <c r="G735" t="n">
+        <v>0</v>
+      </c>
+      <c r="H735" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D736" t="n">
+        <v>0</v>
+      </c>
+      <c r="E736" t="n">
+        <v>0</v>
+      </c>
+      <c r="F736" t="n">
+        <v>0</v>
+      </c>
+      <c r="G736" t="n">
+        <v>0</v>
+      </c>
+      <c r="H736" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D737" t="n">
+        <v>0</v>
+      </c>
+      <c r="E737" t="n">
+        <v>0</v>
+      </c>
+      <c r="F737" t="n">
+        <v>0</v>
+      </c>
+      <c r="G737" t="n">
+        <v>0</v>
+      </c>
+      <c r="H737" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D738" t="n">
+        <v>0</v>
+      </c>
+      <c r="E738" t="n">
+        <v>0</v>
+      </c>
+      <c r="F738" t="n">
+        <v>0</v>
+      </c>
+      <c r="G738" t="n">
+        <v>0</v>
+      </c>
+      <c r="H738" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>0</v>
+      </c>
+      <c r="D739" t="n">
+        <v>0</v>
+      </c>
+      <c r="E739" t="n">
+        <v>0</v>
+      </c>
+      <c r="F739" t="n">
+        <v>0</v>
+      </c>
+      <c r="G739" t="n">
+        <v>0</v>
+      </c>
+      <c r="H739" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D740" t="n">
+        <v>0</v>
+      </c>
+      <c r="E740" t="n">
+        <v>0</v>
+      </c>
+      <c r="F740" t="n">
+        <v>0</v>
+      </c>
+      <c r="G740" t="n">
+        <v>0</v>
+      </c>
+      <c r="H740" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>75944.144</v>
+      </c>
+      <c r="D741" t="n">
+        <v>0</v>
+      </c>
+      <c r="E741" t="n">
+        <v>0</v>
+      </c>
+      <c r="F741" t="n">
+        <v>0</v>
+      </c>
+      <c r="G741" t="n">
+        <v>0</v>
+      </c>
+      <c r="H741" t="n">
+        <v>75944.144</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D742" t="n">
+        <v>0</v>
+      </c>
+      <c r="E742" t="n">
+        <v>0</v>
+      </c>
+      <c r="F742" t="n">
+        <v>0</v>
+      </c>
+      <c r="G742" t="n">
+        <v>0</v>
+      </c>
+      <c r="H742" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>70953.296</v>
+      </c>
+      <c r="D743" t="n">
+        <v>0</v>
+      </c>
+      <c r="E743" t="n">
+        <v>0</v>
+      </c>
+      <c r="F743" t="n">
+        <v>0</v>
+      </c>
+      <c r="G743" t="n">
+        <v>0</v>
+      </c>
+      <c r="H743" t="n">
+        <v>70953.296</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D744" t="n">
+        <v>0</v>
+      </c>
+      <c r="E744" t="n">
+        <v>0</v>
+      </c>
+      <c r="F744" t="n">
+        <v>0</v>
+      </c>
+      <c r="G744" t="n">
+        <v>0</v>
+      </c>
+      <c r="H744" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>0</v>
+      </c>
+      <c r="D745" t="n">
+        <v>0</v>
+      </c>
+      <c r="E745" t="n">
+        <v>0</v>
+      </c>
+      <c r="F745" t="n">
+        <v>0</v>
+      </c>
+      <c r="G745" t="n">
+        <v>0</v>
+      </c>
+      <c r="H745" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D746" t="n">
+        <v>0</v>
+      </c>
+      <c r="E746" t="n">
+        <v>0</v>
+      </c>
+      <c r="F746" t="n">
+        <v>0</v>
+      </c>
+      <c r="G746" t="n">
+        <v>0</v>
+      </c>
+      <c r="H746" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>3432.284</v>
+      </c>
+      <c r="D747" t="n">
+        <v>0</v>
+      </c>
+      <c r="E747" t="n">
+        <v>0</v>
+      </c>
+      <c r="F747" t="n">
+        <v>0</v>
+      </c>
+      <c r="G747" t="n">
+        <v>0</v>
+      </c>
+      <c r="H747" t="n">
+        <v>3432.284</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D748" t="n">
+        <v>0</v>
+      </c>
+      <c r="E748" t="n">
+        <v>0</v>
+      </c>
+      <c r="F748" t="n">
+        <v>0</v>
+      </c>
+      <c r="G748" t="n">
+        <v>0</v>
+      </c>
+      <c r="H748" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D749" t="n">
+        <v>0</v>
+      </c>
+      <c r="E749" t="n">
+        <v>0</v>
+      </c>
+      <c r="F749" t="n">
+        <v>0</v>
+      </c>
+      <c r="G749" t="n">
+        <v>0</v>
+      </c>
+      <c r="H749" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H749"/>
+  <dimension ref="A1:H771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21417,6 +21417,622 @@
         <v>0</v>
       </c>
       <c r="H749" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>0</v>
+      </c>
+      <c r="D750" t="n">
+        <v>0</v>
+      </c>
+      <c r="E750" t="n">
+        <v>0</v>
+      </c>
+      <c r="F750" t="n">
+        <v>0</v>
+      </c>
+      <c r="G750" t="n">
+        <v>0</v>
+      </c>
+      <c r="H750" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>0</v>
+      </c>
+      <c r="D751" t="n">
+        <v>0</v>
+      </c>
+      <c r="E751" t="n">
+        <v>0</v>
+      </c>
+      <c r="F751" t="n">
+        <v>0</v>
+      </c>
+      <c r="G751" t="n">
+        <v>0</v>
+      </c>
+      <c r="H751" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D752" t="n">
+        <v>0</v>
+      </c>
+      <c r="E752" t="n">
+        <v>0</v>
+      </c>
+      <c r="F752" t="n">
+        <v>0</v>
+      </c>
+      <c r="G752" t="n">
+        <v>0</v>
+      </c>
+      <c r="H752" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>86539.92200000001</v>
+      </c>
+      <c r="D753" t="n">
+        <v>0</v>
+      </c>
+      <c r="E753" t="n">
+        <v>0</v>
+      </c>
+      <c r="F753" t="n">
+        <v>0</v>
+      </c>
+      <c r="G753" t="n">
+        <v>0</v>
+      </c>
+      <c r="H753" t="n">
+        <v>86539.92200000001</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D754" t="n">
+        <v>0</v>
+      </c>
+      <c r="E754" t="n">
+        <v>0</v>
+      </c>
+      <c r="F754" t="n">
+        <v>0</v>
+      </c>
+      <c r="G754" t="n">
+        <v>0</v>
+      </c>
+      <c r="H754" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>0</v>
+      </c>
+      <c r="D755" t="n">
+        <v>0</v>
+      </c>
+      <c r="E755" t="n">
+        <v>0</v>
+      </c>
+      <c r="F755" t="n">
+        <v>0</v>
+      </c>
+      <c r="G755" t="n">
+        <v>0</v>
+      </c>
+      <c r="H755" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D756" t="n">
+        <v>0</v>
+      </c>
+      <c r="E756" t="n">
+        <v>0</v>
+      </c>
+      <c r="F756" t="n">
+        <v>0</v>
+      </c>
+      <c r="G756" t="n">
+        <v>0</v>
+      </c>
+      <c r="H756" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D757" t="n">
+        <v>0</v>
+      </c>
+      <c r="E757" t="n">
+        <v>0</v>
+      </c>
+      <c r="F757" t="n">
+        <v>0</v>
+      </c>
+      <c r="G757" t="n">
+        <v>0</v>
+      </c>
+      <c r="H757" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D758" t="n">
+        <v>0</v>
+      </c>
+      <c r="E758" t="n">
+        <v>0</v>
+      </c>
+      <c r="F758" t="n">
+        <v>0</v>
+      </c>
+      <c r="G758" t="n">
+        <v>0</v>
+      </c>
+      <c r="H758" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D759" t="n">
+        <v>0</v>
+      </c>
+      <c r="E759" t="n">
+        <v>0</v>
+      </c>
+      <c r="F759" t="n">
+        <v>0</v>
+      </c>
+      <c r="G759" t="n">
+        <v>0</v>
+      </c>
+      <c r="H759" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D760" t="n">
+        <v>0</v>
+      </c>
+      <c r="E760" t="n">
+        <v>0</v>
+      </c>
+      <c r="F760" t="n">
+        <v>0</v>
+      </c>
+      <c r="G760" t="n">
+        <v>0</v>
+      </c>
+      <c r="H760" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>0</v>
+      </c>
+      <c r="D761" t="n">
+        <v>0</v>
+      </c>
+      <c r="E761" t="n">
+        <v>0</v>
+      </c>
+      <c r="F761" t="n">
+        <v>0</v>
+      </c>
+      <c r="G761" t="n">
+        <v>0</v>
+      </c>
+      <c r="H761" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D762" t="n">
+        <v>0</v>
+      </c>
+      <c r="E762" t="n">
+        <v>0</v>
+      </c>
+      <c r="F762" t="n">
+        <v>0</v>
+      </c>
+      <c r="G762" t="n">
+        <v>0</v>
+      </c>
+      <c r="H762" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>75944.144</v>
+      </c>
+      <c r="D763" t="n">
+        <v>0</v>
+      </c>
+      <c r="E763" t="n">
+        <v>0</v>
+      </c>
+      <c r="F763" t="n">
+        <v>0</v>
+      </c>
+      <c r="G763" t="n">
+        <v>0</v>
+      </c>
+      <c r="H763" t="n">
+        <v>75944.144</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D764" t="n">
+        <v>0</v>
+      </c>
+      <c r="E764" t="n">
+        <v>0</v>
+      </c>
+      <c r="F764" t="n">
+        <v>0</v>
+      </c>
+      <c r="G764" t="n">
+        <v>0</v>
+      </c>
+      <c r="H764" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>70953.296</v>
+      </c>
+      <c r="D765" t="n">
+        <v>0</v>
+      </c>
+      <c r="E765" t="n">
+        <v>0</v>
+      </c>
+      <c r="F765" t="n">
+        <v>0</v>
+      </c>
+      <c r="G765" t="n">
+        <v>0</v>
+      </c>
+      <c r="H765" t="n">
+        <v>70953.296</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D766" t="n">
+        <v>0</v>
+      </c>
+      <c r="E766" t="n">
+        <v>0</v>
+      </c>
+      <c r="F766" t="n">
+        <v>0</v>
+      </c>
+      <c r="G766" t="n">
+        <v>0</v>
+      </c>
+      <c r="H766" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>0</v>
+      </c>
+      <c r="D767" t="n">
+        <v>0</v>
+      </c>
+      <c r="E767" t="n">
+        <v>0</v>
+      </c>
+      <c r="F767" t="n">
+        <v>0</v>
+      </c>
+      <c r="G767" t="n">
+        <v>0</v>
+      </c>
+      <c r="H767" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D768" t="n">
+        <v>0</v>
+      </c>
+      <c r="E768" t="n">
+        <v>0</v>
+      </c>
+      <c r="F768" t="n">
+        <v>0</v>
+      </c>
+      <c r="G768" t="n">
+        <v>0</v>
+      </c>
+      <c r="H768" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>3432.284</v>
+      </c>
+      <c r="D769" t="n">
+        <v>0</v>
+      </c>
+      <c r="E769" t="n">
+        <v>0</v>
+      </c>
+      <c r="F769" t="n">
+        <v>0</v>
+      </c>
+      <c r="G769" t="n">
+        <v>0</v>
+      </c>
+      <c r="H769" t="n">
+        <v>3432.284</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D770" t="n">
+        <v>0</v>
+      </c>
+      <c r="E770" t="n">
+        <v>0</v>
+      </c>
+      <c r="F770" t="n">
+        <v>0</v>
+      </c>
+      <c r="G770" t="n">
+        <v>0</v>
+      </c>
+      <c r="H770" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D771" t="n">
+        <v>0</v>
+      </c>
+      <c r="E771" t="n">
+        <v>0</v>
+      </c>
+      <c r="F771" t="n">
+        <v>0</v>
+      </c>
+      <c r="G771" t="n">
+        <v>0</v>
+      </c>
+      <c r="H771" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H771"/>
+  <dimension ref="A1:H793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22033,6 +22033,622 @@
         <v>0</v>
       </c>
       <c r="H771" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>0</v>
+      </c>
+      <c r="D772" t="n">
+        <v>0</v>
+      </c>
+      <c r="E772" t="n">
+        <v>0</v>
+      </c>
+      <c r="F772" t="n">
+        <v>0</v>
+      </c>
+      <c r="G772" t="n">
+        <v>0</v>
+      </c>
+      <c r="H772" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>0</v>
+      </c>
+      <c r="D773" t="n">
+        <v>0</v>
+      </c>
+      <c r="E773" t="n">
+        <v>0</v>
+      </c>
+      <c r="F773" t="n">
+        <v>0</v>
+      </c>
+      <c r="G773" t="n">
+        <v>0</v>
+      </c>
+      <c r="H773" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D774" t="n">
+        <v>0</v>
+      </c>
+      <c r="E774" t="n">
+        <v>0</v>
+      </c>
+      <c r="F774" t="n">
+        <v>0</v>
+      </c>
+      <c r="G774" t="n">
+        <v>0</v>
+      </c>
+      <c r="H774" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>86539.92200000001</v>
+      </c>
+      <c r="D775" t="n">
+        <v>0</v>
+      </c>
+      <c r="E775" t="n">
+        <v>0</v>
+      </c>
+      <c r="F775" t="n">
+        <v>0</v>
+      </c>
+      <c r="G775" t="n">
+        <v>0</v>
+      </c>
+      <c r="H775" t="n">
+        <v>86539.92200000001</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D776" t="n">
+        <v>0</v>
+      </c>
+      <c r="E776" t="n">
+        <v>0</v>
+      </c>
+      <c r="F776" t="n">
+        <v>0</v>
+      </c>
+      <c r="G776" t="n">
+        <v>0</v>
+      </c>
+      <c r="H776" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>0</v>
+      </c>
+      <c r="D777" t="n">
+        <v>0</v>
+      </c>
+      <c r="E777" t="n">
+        <v>0</v>
+      </c>
+      <c r="F777" t="n">
+        <v>0</v>
+      </c>
+      <c r="G777" t="n">
+        <v>0</v>
+      </c>
+      <c r="H777" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D778" t="n">
+        <v>0</v>
+      </c>
+      <c r="E778" t="n">
+        <v>0</v>
+      </c>
+      <c r="F778" t="n">
+        <v>0</v>
+      </c>
+      <c r="G778" t="n">
+        <v>0</v>
+      </c>
+      <c r="H778" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D779" t="n">
+        <v>0</v>
+      </c>
+      <c r="E779" t="n">
+        <v>0</v>
+      </c>
+      <c r="F779" t="n">
+        <v>0</v>
+      </c>
+      <c r="G779" t="n">
+        <v>0</v>
+      </c>
+      <c r="H779" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D780" t="n">
+        <v>0</v>
+      </c>
+      <c r="E780" t="n">
+        <v>0</v>
+      </c>
+      <c r="F780" t="n">
+        <v>0</v>
+      </c>
+      <c r="G780" t="n">
+        <v>0</v>
+      </c>
+      <c r="H780" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D781" t="n">
+        <v>0</v>
+      </c>
+      <c r="E781" t="n">
+        <v>0</v>
+      </c>
+      <c r="F781" t="n">
+        <v>0</v>
+      </c>
+      <c r="G781" t="n">
+        <v>0</v>
+      </c>
+      <c r="H781" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D782" t="n">
+        <v>0</v>
+      </c>
+      <c r="E782" t="n">
+        <v>0</v>
+      </c>
+      <c r="F782" t="n">
+        <v>0</v>
+      </c>
+      <c r="G782" t="n">
+        <v>0</v>
+      </c>
+      <c r="H782" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>0</v>
+      </c>
+      <c r="D783" t="n">
+        <v>0</v>
+      </c>
+      <c r="E783" t="n">
+        <v>0</v>
+      </c>
+      <c r="F783" t="n">
+        <v>0</v>
+      </c>
+      <c r="G783" t="n">
+        <v>0</v>
+      </c>
+      <c r="H783" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D784" t="n">
+        <v>0</v>
+      </c>
+      <c r="E784" t="n">
+        <v>0</v>
+      </c>
+      <c r="F784" t="n">
+        <v>0</v>
+      </c>
+      <c r="G784" t="n">
+        <v>0</v>
+      </c>
+      <c r="H784" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>75944.144</v>
+      </c>
+      <c r="D785" t="n">
+        <v>0</v>
+      </c>
+      <c r="E785" t="n">
+        <v>0</v>
+      </c>
+      <c r="F785" t="n">
+        <v>0</v>
+      </c>
+      <c r="G785" t="n">
+        <v>0</v>
+      </c>
+      <c r="H785" t="n">
+        <v>75944.144</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D786" t="n">
+        <v>0</v>
+      </c>
+      <c r="E786" t="n">
+        <v>0</v>
+      </c>
+      <c r="F786" t="n">
+        <v>0</v>
+      </c>
+      <c r="G786" t="n">
+        <v>0</v>
+      </c>
+      <c r="H786" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>70953.296</v>
+      </c>
+      <c r="D787" t="n">
+        <v>0</v>
+      </c>
+      <c r="E787" t="n">
+        <v>0</v>
+      </c>
+      <c r="F787" t="n">
+        <v>0</v>
+      </c>
+      <c r="G787" t="n">
+        <v>0</v>
+      </c>
+      <c r="H787" t="n">
+        <v>70953.296</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D788" t="n">
+        <v>0</v>
+      </c>
+      <c r="E788" t="n">
+        <v>0</v>
+      </c>
+      <c r="F788" t="n">
+        <v>0</v>
+      </c>
+      <c r="G788" t="n">
+        <v>0</v>
+      </c>
+      <c r="H788" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>0</v>
+      </c>
+      <c r="D789" t="n">
+        <v>0</v>
+      </c>
+      <c r="E789" t="n">
+        <v>0</v>
+      </c>
+      <c r="F789" t="n">
+        <v>0</v>
+      </c>
+      <c r="G789" t="n">
+        <v>0</v>
+      </c>
+      <c r="H789" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D790" t="n">
+        <v>0</v>
+      </c>
+      <c r="E790" t="n">
+        <v>0</v>
+      </c>
+      <c r="F790" t="n">
+        <v>0</v>
+      </c>
+      <c r="G790" t="n">
+        <v>0</v>
+      </c>
+      <c r="H790" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>3432.284</v>
+      </c>
+      <c r="D791" t="n">
+        <v>0</v>
+      </c>
+      <c r="E791" t="n">
+        <v>0</v>
+      </c>
+      <c r="F791" t="n">
+        <v>0</v>
+      </c>
+      <c r="G791" t="n">
+        <v>0</v>
+      </c>
+      <c r="H791" t="n">
+        <v>3432.284</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D792" t="n">
+        <v>0</v>
+      </c>
+      <c r="E792" t="n">
+        <v>0</v>
+      </c>
+      <c r="F792" t="n">
+        <v>0</v>
+      </c>
+      <c r="G792" t="n">
+        <v>0</v>
+      </c>
+      <c r="H792" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D793" t="n">
+        <v>0</v>
+      </c>
+      <c r="E793" t="n">
+        <v>0</v>
+      </c>
+      <c r="F793" t="n">
+        <v>0</v>
+      </c>
+      <c r="G793" t="n">
+        <v>0</v>
+      </c>
+      <c r="H793" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H793"/>
+  <dimension ref="A1:H815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22649,6 +22649,622 @@
         <v>0</v>
       </c>
       <c r="H793" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>0</v>
+      </c>
+      <c r="D794" t="n">
+        <v>0</v>
+      </c>
+      <c r="E794" t="n">
+        <v>0</v>
+      </c>
+      <c r="F794" t="n">
+        <v>0</v>
+      </c>
+      <c r="G794" t="n">
+        <v>0</v>
+      </c>
+      <c r="H794" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>0</v>
+      </c>
+      <c r="D795" t="n">
+        <v>0</v>
+      </c>
+      <c r="E795" t="n">
+        <v>0</v>
+      </c>
+      <c r="F795" t="n">
+        <v>0</v>
+      </c>
+      <c r="G795" t="n">
+        <v>0</v>
+      </c>
+      <c r="H795" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D796" t="n">
+        <v>0</v>
+      </c>
+      <c r="E796" t="n">
+        <v>0</v>
+      </c>
+      <c r="F796" t="n">
+        <v>0</v>
+      </c>
+      <c r="G796" t="n">
+        <v>0</v>
+      </c>
+      <c r="H796" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>86539.92200000001</v>
+      </c>
+      <c r="D797" t="n">
+        <v>0</v>
+      </c>
+      <c r="E797" t="n">
+        <v>0</v>
+      </c>
+      <c r="F797" t="n">
+        <v>0</v>
+      </c>
+      <c r="G797" t="n">
+        <v>0</v>
+      </c>
+      <c r="H797" t="n">
+        <v>86539.92200000001</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D798" t="n">
+        <v>0</v>
+      </c>
+      <c r="E798" t="n">
+        <v>0</v>
+      </c>
+      <c r="F798" t="n">
+        <v>0</v>
+      </c>
+      <c r="G798" t="n">
+        <v>0</v>
+      </c>
+      <c r="H798" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>0</v>
+      </c>
+      <c r="D799" t="n">
+        <v>0</v>
+      </c>
+      <c r="E799" t="n">
+        <v>0</v>
+      </c>
+      <c r="F799" t="n">
+        <v>0</v>
+      </c>
+      <c r="G799" t="n">
+        <v>0</v>
+      </c>
+      <c r="H799" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D800" t="n">
+        <v>0</v>
+      </c>
+      <c r="E800" t="n">
+        <v>0</v>
+      </c>
+      <c r="F800" t="n">
+        <v>0</v>
+      </c>
+      <c r="G800" t="n">
+        <v>0</v>
+      </c>
+      <c r="H800" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D801" t="n">
+        <v>0</v>
+      </c>
+      <c r="E801" t="n">
+        <v>0</v>
+      </c>
+      <c r="F801" t="n">
+        <v>0</v>
+      </c>
+      <c r="G801" t="n">
+        <v>0</v>
+      </c>
+      <c r="H801" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D802" t="n">
+        <v>0</v>
+      </c>
+      <c r="E802" t="n">
+        <v>0</v>
+      </c>
+      <c r="F802" t="n">
+        <v>0</v>
+      </c>
+      <c r="G802" t="n">
+        <v>0</v>
+      </c>
+      <c r="H802" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D803" t="n">
+        <v>0</v>
+      </c>
+      <c r="E803" t="n">
+        <v>0</v>
+      </c>
+      <c r="F803" t="n">
+        <v>0</v>
+      </c>
+      <c r="G803" t="n">
+        <v>0</v>
+      </c>
+      <c r="H803" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D804" t="n">
+        <v>0</v>
+      </c>
+      <c r="E804" t="n">
+        <v>0</v>
+      </c>
+      <c r="F804" t="n">
+        <v>0</v>
+      </c>
+      <c r="G804" t="n">
+        <v>0</v>
+      </c>
+      <c r="H804" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>0</v>
+      </c>
+      <c r="D805" t="n">
+        <v>0</v>
+      </c>
+      <c r="E805" t="n">
+        <v>0</v>
+      </c>
+      <c r="F805" t="n">
+        <v>0</v>
+      </c>
+      <c r="G805" t="n">
+        <v>0</v>
+      </c>
+      <c r="H805" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D806" t="n">
+        <v>0</v>
+      </c>
+      <c r="E806" t="n">
+        <v>0</v>
+      </c>
+      <c r="F806" t="n">
+        <v>0</v>
+      </c>
+      <c r="G806" t="n">
+        <v>0</v>
+      </c>
+      <c r="H806" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>75944.144</v>
+      </c>
+      <c r="D807" t="n">
+        <v>0</v>
+      </c>
+      <c r="E807" t="n">
+        <v>459.633</v>
+      </c>
+      <c r="F807" t="n">
+        <v>-459.633</v>
+      </c>
+      <c r="G807" t="n">
+        <v>0</v>
+      </c>
+      <c r="H807" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D808" t="n">
+        <v>0</v>
+      </c>
+      <c r="E808" t="n">
+        <v>0</v>
+      </c>
+      <c r="F808" t="n">
+        <v>0</v>
+      </c>
+      <c r="G808" t="n">
+        <v>0</v>
+      </c>
+      <c r="H808" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>70953.296</v>
+      </c>
+      <c r="D809" t="n">
+        <v>0</v>
+      </c>
+      <c r="E809" t="n">
+        <v>0</v>
+      </c>
+      <c r="F809" t="n">
+        <v>0</v>
+      </c>
+      <c r="G809" t="n">
+        <v>0</v>
+      </c>
+      <c r="H809" t="n">
+        <v>70953.296</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D810" t="n">
+        <v>0</v>
+      </c>
+      <c r="E810" t="n">
+        <v>0</v>
+      </c>
+      <c r="F810" t="n">
+        <v>0</v>
+      </c>
+      <c r="G810" t="n">
+        <v>0</v>
+      </c>
+      <c r="H810" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>0</v>
+      </c>
+      <c r="D811" t="n">
+        <v>0</v>
+      </c>
+      <c r="E811" t="n">
+        <v>0</v>
+      </c>
+      <c r="F811" t="n">
+        <v>0</v>
+      </c>
+      <c r="G811" t="n">
+        <v>0</v>
+      </c>
+      <c r="H811" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D812" t="n">
+        <v>0</v>
+      </c>
+      <c r="E812" t="n">
+        <v>0</v>
+      </c>
+      <c r="F812" t="n">
+        <v>0</v>
+      </c>
+      <c r="G812" t="n">
+        <v>0</v>
+      </c>
+      <c r="H812" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>3432.284</v>
+      </c>
+      <c r="D813" t="n">
+        <v>0</v>
+      </c>
+      <c r="E813" t="n">
+        <v>0</v>
+      </c>
+      <c r="F813" t="n">
+        <v>0</v>
+      </c>
+      <c r="G813" t="n">
+        <v>0</v>
+      </c>
+      <c r="H813" t="n">
+        <v>3432.284</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D814" t="n">
+        <v>0</v>
+      </c>
+      <c r="E814" t="n">
+        <v>0</v>
+      </c>
+      <c r="F814" t="n">
+        <v>0</v>
+      </c>
+      <c r="G814" t="n">
+        <v>0</v>
+      </c>
+      <c r="H814" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D815" t="n">
+        <v>0</v>
+      </c>
+      <c r="E815" t="n">
+        <v>0</v>
+      </c>
+      <c r="F815" t="n">
+        <v>0</v>
+      </c>
+      <c r="G815" t="n">
+        <v>0</v>
+      </c>
+      <c r="H815" t="n">
         <v>16.075</v>
       </c>
     </row>
@@ -22791,13 +23407,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75944.144</v>
+        <v>75484.511</v>
       </c>
       <c r="C8" t="n">
         <v>113601.788</v>
       </c>
       <c r="D8" t="n">
-        <v>189545.932</v>
+        <v>189086.299</v>
       </c>
     </row>
     <row r="9">
@@ -22907,13 +23523,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>264627.284</v>
+        <v>264167.651</v>
       </c>
       <c r="C2" t="n">
         <v>313567.939</v>
       </c>
       <c r="D2" t="n">
-        <v>578195.223</v>
+        <v>577735.5900000001</v>
       </c>
     </row>
     <row r="3">
@@ -23233,10 +23849,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>924.158</v>
+        <v>1383.791</v>
       </c>
       <c r="E20" t="n">
-        <v>75944.144</v>
+        <v>75484.511</v>
       </c>
     </row>
     <row r="21">

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H815"/>
+  <dimension ref="A1:H837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23265,6 +23265,622 @@
         <v>0</v>
       </c>
       <c r="H815" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>0</v>
+      </c>
+      <c r="D816" t="n">
+        <v>0</v>
+      </c>
+      <c r="E816" t="n">
+        <v>0</v>
+      </c>
+      <c r="F816" t="n">
+        <v>0</v>
+      </c>
+      <c r="G816" t="n">
+        <v>0</v>
+      </c>
+      <c r="H816" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>0</v>
+      </c>
+      <c r="D817" t="n">
+        <v>0</v>
+      </c>
+      <c r="E817" t="n">
+        <v>0</v>
+      </c>
+      <c r="F817" t="n">
+        <v>0</v>
+      </c>
+      <c r="G817" t="n">
+        <v>0</v>
+      </c>
+      <c r="H817" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D818" t="n">
+        <v>0</v>
+      </c>
+      <c r="E818" t="n">
+        <v>0</v>
+      </c>
+      <c r="F818" t="n">
+        <v>0</v>
+      </c>
+      <c r="G818" t="n">
+        <v>0</v>
+      </c>
+      <c r="H818" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>86539.92200000001</v>
+      </c>
+      <c r="D819" t="n">
+        <v>0</v>
+      </c>
+      <c r="E819" t="n">
+        <v>0</v>
+      </c>
+      <c r="F819" t="n">
+        <v>0</v>
+      </c>
+      <c r="G819" t="n">
+        <v>0</v>
+      </c>
+      <c r="H819" t="n">
+        <v>86539.92200000001</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D820" t="n">
+        <v>0</v>
+      </c>
+      <c r="E820" t="n">
+        <v>0</v>
+      </c>
+      <c r="F820" t="n">
+        <v>0</v>
+      </c>
+      <c r="G820" t="n">
+        <v>0</v>
+      </c>
+      <c r="H820" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>0</v>
+      </c>
+      <c r="D821" t="n">
+        <v>0</v>
+      </c>
+      <c r="E821" t="n">
+        <v>0</v>
+      </c>
+      <c r="F821" t="n">
+        <v>0</v>
+      </c>
+      <c r="G821" t="n">
+        <v>0</v>
+      </c>
+      <c r="H821" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D822" t="n">
+        <v>0</v>
+      </c>
+      <c r="E822" t="n">
+        <v>0</v>
+      </c>
+      <c r="F822" t="n">
+        <v>0</v>
+      </c>
+      <c r="G822" t="n">
+        <v>0</v>
+      </c>
+      <c r="H822" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D823" t="n">
+        <v>0</v>
+      </c>
+      <c r="E823" t="n">
+        <v>0</v>
+      </c>
+      <c r="F823" t="n">
+        <v>0</v>
+      </c>
+      <c r="G823" t="n">
+        <v>0</v>
+      </c>
+      <c r="H823" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D824" t="n">
+        <v>0</v>
+      </c>
+      <c r="E824" t="n">
+        <v>0</v>
+      </c>
+      <c r="F824" t="n">
+        <v>0</v>
+      </c>
+      <c r="G824" t="n">
+        <v>0</v>
+      </c>
+      <c r="H824" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D825" t="n">
+        <v>0</v>
+      </c>
+      <c r="E825" t="n">
+        <v>0</v>
+      </c>
+      <c r="F825" t="n">
+        <v>0</v>
+      </c>
+      <c r="G825" t="n">
+        <v>0</v>
+      </c>
+      <c r="H825" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D826" t="n">
+        <v>0</v>
+      </c>
+      <c r="E826" t="n">
+        <v>0</v>
+      </c>
+      <c r="F826" t="n">
+        <v>0</v>
+      </c>
+      <c r="G826" t="n">
+        <v>0</v>
+      </c>
+      <c r="H826" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>0</v>
+      </c>
+      <c r="D827" t="n">
+        <v>0</v>
+      </c>
+      <c r="E827" t="n">
+        <v>0</v>
+      </c>
+      <c r="F827" t="n">
+        <v>0</v>
+      </c>
+      <c r="G827" t="n">
+        <v>0</v>
+      </c>
+      <c r="H827" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D828" t="n">
+        <v>0</v>
+      </c>
+      <c r="E828" t="n">
+        <v>0</v>
+      </c>
+      <c r="F828" t="n">
+        <v>0</v>
+      </c>
+      <c r="G828" t="n">
+        <v>0</v>
+      </c>
+      <c r="H828" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D829" t="n">
+        <v>0</v>
+      </c>
+      <c r="E829" t="n">
+        <v>0</v>
+      </c>
+      <c r="F829" t="n">
+        <v>0</v>
+      </c>
+      <c r="G829" t="n">
+        <v>0</v>
+      </c>
+      <c r="H829" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D830" t="n">
+        <v>0</v>
+      </c>
+      <c r="E830" t="n">
+        <v>0</v>
+      </c>
+      <c r="F830" t="n">
+        <v>0</v>
+      </c>
+      <c r="G830" t="n">
+        <v>0</v>
+      </c>
+      <c r="H830" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>70953.296</v>
+      </c>
+      <c r="D831" t="n">
+        <v>10330.354</v>
+      </c>
+      <c r="E831" t="n">
+        <v>0</v>
+      </c>
+      <c r="F831" t="n">
+        <v>10330.354</v>
+      </c>
+      <c r="G831" t="n">
+        <v>0</v>
+      </c>
+      <c r="H831" t="n">
+        <v>81283.64999999999</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D832" t="n">
+        <v>0</v>
+      </c>
+      <c r="E832" t="n">
+        <v>0</v>
+      </c>
+      <c r="F832" t="n">
+        <v>0</v>
+      </c>
+      <c r="G832" t="n">
+        <v>0</v>
+      </c>
+      <c r="H832" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>0</v>
+      </c>
+      <c r="D833" t="n">
+        <v>0</v>
+      </c>
+      <c r="E833" t="n">
+        <v>0</v>
+      </c>
+      <c r="F833" t="n">
+        <v>0</v>
+      </c>
+      <c r="G833" t="n">
+        <v>0</v>
+      </c>
+      <c r="H833" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D834" t="n">
+        <v>0</v>
+      </c>
+      <c r="E834" t="n">
+        <v>0</v>
+      </c>
+      <c r="F834" t="n">
+        <v>0</v>
+      </c>
+      <c r="G834" t="n">
+        <v>0</v>
+      </c>
+      <c r="H834" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>3432.284</v>
+      </c>
+      <c r="D835" t="n">
+        <v>0</v>
+      </c>
+      <c r="E835" t="n">
+        <v>0</v>
+      </c>
+      <c r="F835" t="n">
+        <v>0</v>
+      </c>
+      <c r="G835" t="n">
+        <v>0</v>
+      </c>
+      <c r="H835" t="n">
+        <v>3432.284</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D836" t="n">
+        <v>0</v>
+      </c>
+      <c r="E836" t="n">
+        <v>0</v>
+      </c>
+      <c r="F836" t="n">
+        <v>0</v>
+      </c>
+      <c r="G836" t="n">
+        <v>0</v>
+      </c>
+      <c r="H836" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D837" t="n">
+        <v>0</v>
+      </c>
+      <c r="E837" t="n">
+        <v>0</v>
+      </c>
+      <c r="F837" t="n">
+        <v>0</v>
+      </c>
+      <c r="G837" t="n">
+        <v>0</v>
+      </c>
+      <c r="H837" t="n">
         <v>16.075</v>
       </c>
     </row>
@@ -23423,13 +24039,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70953.296</v>
+        <v>81283.64999999999</v>
       </c>
       <c r="C9" t="n">
         <v>59209.788</v>
       </c>
       <c r="D9" t="n">
-        <v>130163.084</v>
+        <v>140493.438</v>
       </c>
     </row>
     <row r="10">
@@ -23523,13 +24139,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>264167.651</v>
+        <v>274498.005</v>
       </c>
       <c r="C2" t="n">
         <v>313567.939</v>
       </c>
       <c r="D2" t="n">
-        <v>577735.5900000001</v>
+        <v>588065.944</v>
       </c>
     </row>
     <row r="3">
@@ -23888,13 +24504,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>10330.354</v>
       </c>
       <c r="D22" t="n">
         <v>65660.113</v>
       </c>
       <c r="E22" t="n">
-        <v>70953.296</v>
+        <v>81283.64999999999</v>
       </c>
     </row>
     <row r="23">

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H837"/>
+  <dimension ref="A1:H859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23881,6 +23881,622 @@
         <v>0</v>
       </c>
       <c r="H837" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>0</v>
+      </c>
+      <c r="D838" t="n">
+        <v>0</v>
+      </c>
+      <c r="E838" t="n">
+        <v>0</v>
+      </c>
+      <c r="F838" t="n">
+        <v>0</v>
+      </c>
+      <c r="G838" t="n">
+        <v>0</v>
+      </c>
+      <c r="H838" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>0</v>
+      </c>
+      <c r="D839" t="n">
+        <v>0</v>
+      </c>
+      <c r="E839" t="n">
+        <v>0</v>
+      </c>
+      <c r="F839" t="n">
+        <v>0</v>
+      </c>
+      <c r="G839" t="n">
+        <v>0</v>
+      </c>
+      <c r="H839" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D840" t="n">
+        <v>0</v>
+      </c>
+      <c r="E840" t="n">
+        <v>0</v>
+      </c>
+      <c r="F840" t="n">
+        <v>0</v>
+      </c>
+      <c r="G840" t="n">
+        <v>0</v>
+      </c>
+      <c r="H840" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>86539.92200000001</v>
+      </c>
+      <c r="D841" t="n">
+        <v>0</v>
+      </c>
+      <c r="E841" t="n">
+        <v>907.41</v>
+      </c>
+      <c r="F841" t="n">
+        <v>-907.41</v>
+      </c>
+      <c r="G841" t="n">
+        <v>0</v>
+      </c>
+      <c r="H841" t="n">
+        <v>85632.512</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D842" t="n">
+        <v>0</v>
+      </c>
+      <c r="E842" t="n">
+        <v>0</v>
+      </c>
+      <c r="F842" t="n">
+        <v>0</v>
+      </c>
+      <c r="G842" t="n">
+        <v>0</v>
+      </c>
+      <c r="H842" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>0</v>
+      </c>
+      <c r="D843" t="n">
+        <v>0</v>
+      </c>
+      <c r="E843" t="n">
+        <v>0</v>
+      </c>
+      <c r="F843" t="n">
+        <v>0</v>
+      </c>
+      <c r="G843" t="n">
+        <v>0</v>
+      </c>
+      <c r="H843" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D844" t="n">
+        <v>0</v>
+      </c>
+      <c r="E844" t="n">
+        <v>0</v>
+      </c>
+      <c r="F844" t="n">
+        <v>0</v>
+      </c>
+      <c r="G844" t="n">
+        <v>0</v>
+      </c>
+      <c r="H844" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D845" t="n">
+        <v>0</v>
+      </c>
+      <c r="E845" t="n">
+        <v>0</v>
+      </c>
+      <c r="F845" t="n">
+        <v>0</v>
+      </c>
+      <c r="G845" t="n">
+        <v>0</v>
+      </c>
+      <c r="H845" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D846" t="n">
+        <v>0</v>
+      </c>
+      <c r="E846" t="n">
+        <v>0</v>
+      </c>
+      <c r="F846" t="n">
+        <v>0</v>
+      </c>
+      <c r="G846" t="n">
+        <v>0</v>
+      </c>
+      <c r="H846" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D847" t="n">
+        <v>0</v>
+      </c>
+      <c r="E847" t="n">
+        <v>0</v>
+      </c>
+      <c r="F847" t="n">
+        <v>0</v>
+      </c>
+      <c r="G847" t="n">
+        <v>0</v>
+      </c>
+      <c r="H847" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D848" t="n">
+        <v>0</v>
+      </c>
+      <c r="E848" t="n">
+        <v>0</v>
+      </c>
+      <c r="F848" t="n">
+        <v>0</v>
+      </c>
+      <c r="G848" t="n">
+        <v>0</v>
+      </c>
+      <c r="H848" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>0</v>
+      </c>
+      <c r="D849" t="n">
+        <v>0</v>
+      </c>
+      <c r="E849" t="n">
+        <v>0</v>
+      </c>
+      <c r="F849" t="n">
+        <v>0</v>
+      </c>
+      <c r="G849" t="n">
+        <v>0</v>
+      </c>
+      <c r="H849" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D850" t="n">
+        <v>0</v>
+      </c>
+      <c r="E850" t="n">
+        <v>0</v>
+      </c>
+      <c r="F850" t="n">
+        <v>0</v>
+      </c>
+      <c r="G850" t="n">
+        <v>0</v>
+      </c>
+      <c r="H850" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D851" t="n">
+        <v>0</v>
+      </c>
+      <c r="E851" t="n">
+        <v>0</v>
+      </c>
+      <c r="F851" t="n">
+        <v>0</v>
+      </c>
+      <c r="G851" t="n">
+        <v>0</v>
+      </c>
+      <c r="H851" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D852" t="n">
+        <v>0</v>
+      </c>
+      <c r="E852" t="n">
+        <v>0</v>
+      </c>
+      <c r="F852" t="n">
+        <v>0</v>
+      </c>
+      <c r="G852" t="n">
+        <v>0</v>
+      </c>
+      <c r="H852" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>81283.64999999999</v>
+      </c>
+      <c r="D853" t="n">
+        <v>0</v>
+      </c>
+      <c r="E853" t="n">
+        <v>0</v>
+      </c>
+      <c r="F853" t="n">
+        <v>0</v>
+      </c>
+      <c r="G853" t="n">
+        <v>0</v>
+      </c>
+      <c r="H853" t="n">
+        <v>81283.64999999999</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D854" t="n">
+        <v>0</v>
+      </c>
+      <c r="E854" t="n">
+        <v>0</v>
+      </c>
+      <c r="F854" t="n">
+        <v>0</v>
+      </c>
+      <c r="G854" t="n">
+        <v>0</v>
+      </c>
+      <c r="H854" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>0</v>
+      </c>
+      <c r="D855" t="n">
+        <v>0</v>
+      </c>
+      <c r="E855" t="n">
+        <v>0</v>
+      </c>
+      <c r="F855" t="n">
+        <v>0</v>
+      </c>
+      <c r="G855" t="n">
+        <v>0</v>
+      </c>
+      <c r="H855" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D856" t="n">
+        <v>0</v>
+      </c>
+      <c r="E856" t="n">
+        <v>0</v>
+      </c>
+      <c r="F856" t="n">
+        <v>0</v>
+      </c>
+      <c r="G856" t="n">
+        <v>0</v>
+      </c>
+      <c r="H856" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>3432.284</v>
+      </c>
+      <c r="D857" t="n">
+        <v>0</v>
+      </c>
+      <c r="E857" t="n">
+        <v>0</v>
+      </c>
+      <c r="F857" t="n">
+        <v>0</v>
+      </c>
+      <c r="G857" t="n">
+        <v>0</v>
+      </c>
+      <c r="H857" t="n">
+        <v>3432.284</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D858" t="n">
+        <v>0</v>
+      </c>
+      <c r="E858" t="n">
+        <v>0</v>
+      </c>
+      <c r="F858" t="n">
+        <v>0</v>
+      </c>
+      <c r="G858" t="n">
+        <v>0</v>
+      </c>
+      <c r="H858" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D859" t="n">
+        <v>0</v>
+      </c>
+      <c r="E859" t="n">
+        <v>0</v>
+      </c>
+      <c r="F859" t="n">
+        <v>0</v>
+      </c>
+      <c r="G859" t="n">
+        <v>0</v>
+      </c>
+      <c r="H859" t="n">
         <v>16.075</v>
       </c>
     </row>
@@ -23943,13 +24559,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86539.92200000001</v>
+        <v>85632.512</v>
       </c>
       <c r="C3" t="n">
         <v>71275.599</v>
       </c>
       <c r="D3" t="n">
-        <v>157815.521</v>
+        <v>156908.111</v>
       </c>
     </row>
     <row r="4">
@@ -24139,13 +24755,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>274498.005</v>
+        <v>273590.595</v>
       </c>
       <c r="C2" t="n">
         <v>313567.939</v>
       </c>
       <c r="D2" t="n">
-        <v>588065.944</v>
+        <v>587158.534</v>
       </c>
     </row>
     <row r="3">
@@ -24255,10 +24871,10 @@
         <v>56826.488</v>
       </c>
       <c r="D10" t="n">
-        <v>17539.066</v>
+        <v>18446.476</v>
       </c>
       <c r="E10" t="n">
-        <v>86539.92200000001</v>
+        <v>85632.512</v>
       </c>
     </row>
     <row r="11">

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H859"/>
+  <dimension ref="A1:H881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24497,6 +24497,622 @@
         <v>0</v>
       </c>
       <c r="H859" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>0</v>
+      </c>
+      <c r="D860" t="n">
+        <v>0</v>
+      </c>
+      <c r="E860" t="n">
+        <v>0</v>
+      </c>
+      <c r="F860" t="n">
+        <v>0</v>
+      </c>
+      <c r="G860" t="n">
+        <v>0</v>
+      </c>
+      <c r="H860" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>0</v>
+      </c>
+      <c r="D861" t="n">
+        <v>0</v>
+      </c>
+      <c r="E861" t="n">
+        <v>0</v>
+      </c>
+      <c r="F861" t="n">
+        <v>0</v>
+      </c>
+      <c r="G861" t="n">
+        <v>0</v>
+      </c>
+      <c r="H861" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D862" t="n">
+        <v>0</v>
+      </c>
+      <c r="E862" t="n">
+        <v>0</v>
+      </c>
+      <c r="F862" t="n">
+        <v>0</v>
+      </c>
+      <c r="G862" t="n">
+        <v>0</v>
+      </c>
+      <c r="H862" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>85632.512</v>
+      </c>
+      <c r="D863" t="n">
+        <v>0</v>
+      </c>
+      <c r="E863" t="n">
+        <v>0</v>
+      </c>
+      <c r="F863" t="n">
+        <v>0</v>
+      </c>
+      <c r="G863" t="n">
+        <v>0</v>
+      </c>
+      <c r="H863" t="n">
+        <v>85632.512</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D864" t="n">
+        <v>0</v>
+      </c>
+      <c r="E864" t="n">
+        <v>0</v>
+      </c>
+      <c r="F864" t="n">
+        <v>0</v>
+      </c>
+      <c r="G864" t="n">
+        <v>0</v>
+      </c>
+      <c r="H864" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>0</v>
+      </c>
+      <c r="D865" t="n">
+        <v>0</v>
+      </c>
+      <c r="E865" t="n">
+        <v>0</v>
+      </c>
+      <c r="F865" t="n">
+        <v>0</v>
+      </c>
+      <c r="G865" t="n">
+        <v>0</v>
+      </c>
+      <c r="H865" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D866" t="n">
+        <v>0</v>
+      </c>
+      <c r="E866" t="n">
+        <v>0</v>
+      </c>
+      <c r="F866" t="n">
+        <v>0</v>
+      </c>
+      <c r="G866" t="n">
+        <v>0</v>
+      </c>
+      <c r="H866" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D867" t="n">
+        <v>0</v>
+      </c>
+      <c r="E867" t="n">
+        <v>0</v>
+      </c>
+      <c r="F867" t="n">
+        <v>0</v>
+      </c>
+      <c r="G867" t="n">
+        <v>0</v>
+      </c>
+      <c r="H867" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D868" t="n">
+        <v>0</v>
+      </c>
+      <c r="E868" t="n">
+        <v>0</v>
+      </c>
+      <c r="F868" t="n">
+        <v>0</v>
+      </c>
+      <c r="G868" t="n">
+        <v>0</v>
+      </c>
+      <c r="H868" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D869" t="n">
+        <v>0</v>
+      </c>
+      <c r="E869" t="n">
+        <v>0</v>
+      </c>
+      <c r="F869" t="n">
+        <v>0</v>
+      </c>
+      <c r="G869" t="n">
+        <v>0</v>
+      </c>
+      <c r="H869" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D870" t="n">
+        <v>0</v>
+      </c>
+      <c r="E870" t="n">
+        <v>0</v>
+      </c>
+      <c r="F870" t="n">
+        <v>0</v>
+      </c>
+      <c r="G870" t="n">
+        <v>0</v>
+      </c>
+      <c r="H870" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>0</v>
+      </c>
+      <c r="D871" t="n">
+        <v>0</v>
+      </c>
+      <c r="E871" t="n">
+        <v>0</v>
+      </c>
+      <c r="F871" t="n">
+        <v>0</v>
+      </c>
+      <c r="G871" t="n">
+        <v>0</v>
+      </c>
+      <c r="H871" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D872" t="n">
+        <v>0</v>
+      </c>
+      <c r="E872" t="n">
+        <v>0</v>
+      </c>
+      <c r="F872" t="n">
+        <v>0</v>
+      </c>
+      <c r="G872" t="n">
+        <v>0</v>
+      </c>
+      <c r="H872" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D873" t="n">
+        <v>0</v>
+      </c>
+      <c r="E873" t="n">
+        <v>0</v>
+      </c>
+      <c r="F873" t="n">
+        <v>0</v>
+      </c>
+      <c r="G873" t="n">
+        <v>0</v>
+      </c>
+      <c r="H873" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D874" t="n">
+        <v>0</v>
+      </c>
+      <c r="E874" t="n">
+        <v>0</v>
+      </c>
+      <c r="F874" t="n">
+        <v>0</v>
+      </c>
+      <c r="G874" t="n">
+        <v>0</v>
+      </c>
+      <c r="H874" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>81283.64999999999</v>
+      </c>
+      <c r="D875" t="n">
+        <v>0</v>
+      </c>
+      <c r="E875" t="n">
+        <v>0</v>
+      </c>
+      <c r="F875" t="n">
+        <v>0</v>
+      </c>
+      <c r="G875" t="n">
+        <v>0</v>
+      </c>
+      <c r="H875" t="n">
+        <v>81283.64999999999</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D876" t="n">
+        <v>0</v>
+      </c>
+      <c r="E876" t="n">
+        <v>0</v>
+      </c>
+      <c r="F876" t="n">
+        <v>0</v>
+      </c>
+      <c r="G876" t="n">
+        <v>0</v>
+      </c>
+      <c r="H876" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>0</v>
+      </c>
+      <c r="D877" t="n">
+        <v>0</v>
+      </c>
+      <c r="E877" t="n">
+        <v>0</v>
+      </c>
+      <c r="F877" t="n">
+        <v>0</v>
+      </c>
+      <c r="G877" t="n">
+        <v>0</v>
+      </c>
+      <c r="H877" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D878" t="n">
+        <v>0</v>
+      </c>
+      <c r="E878" t="n">
+        <v>0</v>
+      </c>
+      <c r="F878" t="n">
+        <v>0</v>
+      </c>
+      <c r="G878" t="n">
+        <v>0</v>
+      </c>
+      <c r="H878" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>3432.284</v>
+      </c>
+      <c r="D879" t="n">
+        <v>0</v>
+      </c>
+      <c r="E879" t="n">
+        <v>0</v>
+      </c>
+      <c r="F879" t="n">
+        <v>0</v>
+      </c>
+      <c r="G879" t="n">
+        <v>0</v>
+      </c>
+      <c r="H879" t="n">
+        <v>3432.284</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C880" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D880" t="n">
+        <v>0</v>
+      </c>
+      <c r="E880" t="n">
+        <v>0</v>
+      </c>
+      <c r="F880" t="n">
+        <v>0</v>
+      </c>
+      <c r="G880" t="n">
+        <v>0</v>
+      </c>
+      <c r="H880" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D881" t="n">
+        <v>0</v>
+      </c>
+      <c r="E881" t="n">
+        <v>0</v>
+      </c>
+      <c r="F881" t="n">
+        <v>0</v>
+      </c>
+      <c r="G881" t="n">
+        <v>0</v>
+      </c>
+      <c r="H881" t="n">
         <v>16.075</v>
       </c>
     </row>
@@ -24723,7 +25339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24751,7 +25367,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -24767,83 +25383,78 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>273590.595</v>
+      </c>
+      <c r="C3" t="n">
+        <v>313567.939</v>
+      </c>
+      <c r="D3" t="n">
+        <v>587158.534</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>278620.985</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>326637.949</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>605258.934</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt; [상세] 창고별 월간 입출고 및 기말 재고</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>YearMonth</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Region_Type</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>RECEIVED</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>WITHDRAWN</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>TOTAL_TODAY</t>
         </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ASAHI DEPOSITORY LLC Eligible</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASAHI DEPOSITORY LLC Registered</t>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -24859,33 +25470,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRINK'S, INC. Eligible</t>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>56826.488</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>18446.476</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>85632.512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BRINK'S, INC. Registered</t>
+          <t>BRINK'S, INC. Eligible</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -24895,18 +25506,18 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>71275.599</v>
+        <v>85632.512</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CNT DEPOSITORY, INC. Eligible</t>
+          <t>BRINK'S, INC. Registered</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -24916,18 +25527,18 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>71275.599</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CNT DEPOSITORY, INC. Registered</t>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -24937,18 +25548,18 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1246.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DELAWARE DEPOSITORY Eligible</t>
+          <t>CNT DEPOSITORY, INC. Registered</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -24958,18 +25569,18 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>18459.584</v>
+        <v>1246.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DELAWARE DEPOSITORY Registered</t>
+          <t>DELAWARE DEPOSITORY Eligible</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -24979,18 +25590,18 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1633.941</v>
+        <v>18459.584</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSBC BANK, USA Eligible</t>
+          <t>DELAWARE DEPOSITORY Registered</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -25000,18 +25611,18 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>9281.978999999999</v>
+        <v>1633.941</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HSBC BANK, USA Registered</t>
+          <t>HSBC BANK, USA Eligible</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -25021,18 +25632,18 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1394.758</v>
+        <v>9281.978999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+          <t>HSBC BANK, USA Registered</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -25042,18 +25653,18 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1394.758</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -25063,39 +25674,39 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2395.448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JP MORGAN CHASE BANK NA Eligible</t>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1383.791</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>75484.511</v>
+        <v>2395.448</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JP MORGAN CHASE BANK NA Registered</t>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -25105,39 +25716,39 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>113601.788</v>
+        <v>75484.511</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10330.354</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>65660.113</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>81283.64999999999</v>
+        <v>113601.788</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -25147,18 +25758,18 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>59209.788</v>
+        <v>81283.64999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MALCA-AMIT USA, LLC Eligible</t>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -25168,18 +25779,18 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>59209.788</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MALCA-AMIT USA, LLC Registered</t>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -25189,39 +25800,39 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>395.145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+          <t>MALCA-AMIT USA, LLC Registered</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>533.3099999999999</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>300.172</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>3432.284</v>
+        <v>395.145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -25231,18 +25842,18 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>48292.647</v>
+        <v>3432.284</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -25252,18 +25863,18 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>16.075</v>
+        <v>48292.647</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>STONEX PRECIOUS METALS LLC Registered</t>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -25273,18 +25884,18 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>14122.765</v>
+        <v>16.075</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ASAHI DEPOSITORY LLC Eligible</t>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -25294,18 +25905,18 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>14122.765</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ASAHI DEPOSITORY LLC Registered</t>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -25321,54 +25932,54 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BRINK'S, INC. Eligible</t>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1369.594</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>42030.257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BRINK'S, INC. Registered</t>
+          <t>BRINK'S, INC. Eligible</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>56826.488</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>18446.476</v>
       </c>
       <c r="E33" t="n">
-        <v>76497.842</v>
+        <v>85632.512</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CNT DEPOSITORY, INC. Eligible</t>
+          <t>BRINK'S, INC. Registered</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -25378,18 +25989,18 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>71275.599</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CNT DEPOSITORY, INC. Registered</t>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -25399,39 +26010,39 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1246.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DELAWARE DEPOSITORY Eligible</t>
+          <t>CNT DEPOSITORY, INC. Registered</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>50.145</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>18459.584</v>
+        <v>1246.06</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DELAWARE DEPOSITORY Registered</t>
+          <t>DELAWARE DEPOSITORY Eligible</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -25441,39 +26052,39 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1633.941</v>
+        <v>18459.584</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HSBC BANK, USA Eligible</t>
+          <t>DELAWARE DEPOSITORY Registered</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>99.535</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>9281.978999999999</v>
+        <v>1633.941</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HSBC BANK, USA Registered</t>
+          <t>HSBC BANK, USA Eligible</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -25483,18 +26094,18 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1394.758</v>
+        <v>9281.978999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+          <t>HSBC BANK, USA Registered</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -25504,18 +26115,18 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1394.758</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -25525,102 +26136,102 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>2395.448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JP MORGAN CHASE BANK NA Eligible</t>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>59929.312</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>75484.511</v>
+        <v>2395.448</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JP MORGAN CHASE BANK NA Registered</t>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1383.791</v>
       </c>
       <c r="E43" t="n">
-        <v>114985.579</v>
+        <v>75484.511</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10177.043</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>132077.206</v>
+        <v>113601.788</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>11373.343</v>
+        <v>10330.354</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>65660.113</v>
       </c>
       <c r="E45" t="n">
-        <v>63745.991</v>
+        <v>81283.64999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MALCA-AMIT USA, LLC Eligible</t>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -25630,18 +26241,18 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>59209.788</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MALCA-AMIT USA, LLC Registered</t>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -25651,60 +26262,60 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>395.145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+          <t>MALCA-AMIT USA, LLC Registered</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>37704.598</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1271.373</v>
+        <v>395.145</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>533.3099999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>300.172</v>
       </c>
       <c r="E49" t="n">
-        <v>50220.42</v>
+        <v>3432.284</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -25714,27 +26325,510 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>16.075</v>
+        <v>48292.647</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1369.594</v>
+      </c>
+      <c r="E55" t="n">
+        <v>42030.257</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>76497.842</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>50.145</v>
+      </c>
+      <c r="E59" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>99.535</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>59929.312</v>
+      </c>
+      <c r="E65" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>114985.579</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>10177.043</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>132077.206</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>11373.343</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>63745.991</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>37704.598</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1271.373</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>50220.42</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
         <is>
           <t>STONEX PRECIOUS METALS LLC Registered</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
         <v>14122.765</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H881"/>
+  <dimension ref="A1:H903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25113,6 +25113,622 @@
         <v>0</v>
       </c>
       <c r="H881" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>0</v>
+      </c>
+      <c r="D882" t="n">
+        <v>0</v>
+      </c>
+      <c r="E882" t="n">
+        <v>0</v>
+      </c>
+      <c r="F882" t="n">
+        <v>0</v>
+      </c>
+      <c r="G882" t="n">
+        <v>0</v>
+      </c>
+      <c r="H882" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>0</v>
+      </c>
+      <c r="D883" t="n">
+        <v>0</v>
+      </c>
+      <c r="E883" t="n">
+        <v>0</v>
+      </c>
+      <c r="F883" t="n">
+        <v>0</v>
+      </c>
+      <c r="G883" t="n">
+        <v>0</v>
+      </c>
+      <c r="H883" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D884" t="n">
+        <v>0</v>
+      </c>
+      <c r="E884" t="n">
+        <v>0</v>
+      </c>
+      <c r="F884" t="n">
+        <v>0</v>
+      </c>
+      <c r="G884" t="n">
+        <v>0</v>
+      </c>
+      <c r="H884" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>85632.512</v>
+      </c>
+      <c r="D885" t="n">
+        <v>0</v>
+      </c>
+      <c r="E885" t="n">
+        <v>0</v>
+      </c>
+      <c r="F885" t="n">
+        <v>0</v>
+      </c>
+      <c r="G885" t="n">
+        <v>0</v>
+      </c>
+      <c r="H885" t="n">
+        <v>85632.512</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D886" t="n">
+        <v>0</v>
+      </c>
+      <c r="E886" t="n">
+        <v>0</v>
+      </c>
+      <c r="F886" t="n">
+        <v>0</v>
+      </c>
+      <c r="G886" t="n">
+        <v>0</v>
+      </c>
+      <c r="H886" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>0</v>
+      </c>
+      <c r="D887" t="n">
+        <v>0</v>
+      </c>
+      <c r="E887" t="n">
+        <v>0</v>
+      </c>
+      <c r="F887" t="n">
+        <v>0</v>
+      </c>
+      <c r="G887" t="n">
+        <v>0</v>
+      </c>
+      <c r="H887" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D888" t="n">
+        <v>0</v>
+      </c>
+      <c r="E888" t="n">
+        <v>0</v>
+      </c>
+      <c r="F888" t="n">
+        <v>0</v>
+      </c>
+      <c r="G888" t="n">
+        <v>0</v>
+      </c>
+      <c r="H888" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D889" t="n">
+        <v>0</v>
+      </c>
+      <c r="E889" t="n">
+        <v>0</v>
+      </c>
+      <c r="F889" t="n">
+        <v>0</v>
+      </c>
+      <c r="G889" t="n">
+        <v>0</v>
+      </c>
+      <c r="H889" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D890" t="n">
+        <v>0</v>
+      </c>
+      <c r="E890" t="n">
+        <v>0</v>
+      </c>
+      <c r="F890" t="n">
+        <v>0</v>
+      </c>
+      <c r="G890" t="n">
+        <v>0</v>
+      </c>
+      <c r="H890" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D891" t="n">
+        <v>0</v>
+      </c>
+      <c r="E891" t="n">
+        <v>0</v>
+      </c>
+      <c r="F891" t="n">
+        <v>0</v>
+      </c>
+      <c r="G891" t="n">
+        <v>0</v>
+      </c>
+      <c r="H891" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D892" t="n">
+        <v>0</v>
+      </c>
+      <c r="E892" t="n">
+        <v>0</v>
+      </c>
+      <c r="F892" t="n">
+        <v>0</v>
+      </c>
+      <c r="G892" t="n">
+        <v>0</v>
+      </c>
+      <c r="H892" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>0</v>
+      </c>
+      <c r="D893" t="n">
+        <v>0</v>
+      </c>
+      <c r="E893" t="n">
+        <v>0</v>
+      </c>
+      <c r="F893" t="n">
+        <v>0</v>
+      </c>
+      <c r="G893" t="n">
+        <v>0</v>
+      </c>
+      <c r="H893" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D894" t="n">
+        <v>0</v>
+      </c>
+      <c r="E894" t="n">
+        <v>0</v>
+      </c>
+      <c r="F894" t="n">
+        <v>0</v>
+      </c>
+      <c r="G894" t="n">
+        <v>0</v>
+      </c>
+      <c r="H894" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D895" t="n">
+        <v>0</v>
+      </c>
+      <c r="E895" t="n">
+        <v>0</v>
+      </c>
+      <c r="F895" t="n">
+        <v>0</v>
+      </c>
+      <c r="G895" t="n">
+        <v>0</v>
+      </c>
+      <c r="H895" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D896" t="n">
+        <v>0</v>
+      </c>
+      <c r="E896" t="n">
+        <v>0</v>
+      </c>
+      <c r="F896" t="n">
+        <v>0</v>
+      </c>
+      <c r="G896" t="n">
+        <v>0</v>
+      </c>
+      <c r="H896" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>81283.64999999999</v>
+      </c>
+      <c r="D897" t="n">
+        <v>0</v>
+      </c>
+      <c r="E897" t="n">
+        <v>0</v>
+      </c>
+      <c r="F897" t="n">
+        <v>0</v>
+      </c>
+      <c r="G897" t="n">
+        <v>0</v>
+      </c>
+      <c r="H897" t="n">
+        <v>81283.64999999999</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D898" t="n">
+        <v>0</v>
+      </c>
+      <c r="E898" t="n">
+        <v>0</v>
+      </c>
+      <c r="F898" t="n">
+        <v>0</v>
+      </c>
+      <c r="G898" t="n">
+        <v>0</v>
+      </c>
+      <c r="H898" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>0</v>
+      </c>
+      <c r="D899" t="n">
+        <v>0</v>
+      </c>
+      <c r="E899" t="n">
+        <v>0</v>
+      </c>
+      <c r="F899" t="n">
+        <v>0</v>
+      </c>
+      <c r="G899" t="n">
+        <v>0</v>
+      </c>
+      <c r="H899" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D900" t="n">
+        <v>0</v>
+      </c>
+      <c r="E900" t="n">
+        <v>0</v>
+      </c>
+      <c r="F900" t="n">
+        <v>0</v>
+      </c>
+      <c r="G900" t="n">
+        <v>0</v>
+      </c>
+      <c r="H900" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>3432.284</v>
+      </c>
+      <c r="D901" t="n">
+        <v>0</v>
+      </c>
+      <c r="E901" t="n">
+        <v>1627.601</v>
+      </c>
+      <c r="F901" t="n">
+        <v>-1627.601</v>
+      </c>
+      <c r="G901" t="n">
+        <v>0</v>
+      </c>
+      <c r="H901" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D902" t="n">
+        <v>0</v>
+      </c>
+      <c r="E902" t="n">
+        <v>0</v>
+      </c>
+      <c r="F902" t="n">
+        <v>0</v>
+      </c>
+      <c r="G902" t="n">
+        <v>0</v>
+      </c>
+      <c r="H902" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D903" t="n">
+        <v>0</v>
+      </c>
+      <c r="E903" t="n">
+        <v>0</v>
+      </c>
+      <c r="F903" t="n">
+        <v>0</v>
+      </c>
+      <c r="G903" t="n">
+        <v>0</v>
+      </c>
+      <c r="H903" t="n">
         <v>16.075</v>
       </c>
     </row>
@@ -25303,13 +25919,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3432.284</v>
+        <v>1804.683</v>
       </c>
       <c r="C11" t="n">
         <v>48292.647</v>
       </c>
       <c r="D11" t="n">
-        <v>51724.931</v>
+        <v>50097.32999999999</v>
       </c>
     </row>
     <row r="12">
@@ -25371,13 +25987,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>273590.595</v>
+        <v>271962.994</v>
       </c>
       <c r="C2" t="n">
         <v>313567.939</v>
       </c>
       <c r="D2" t="n">
-        <v>587158.534</v>
+        <v>585530.933</v>
       </c>
     </row>
     <row r="3">
@@ -25839,10 +26455,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1627.601</v>
       </c>
       <c r="E27" t="n">
-        <v>3432.284</v>
+        <v>1804.683</v>
       </c>
     </row>
     <row r="28">

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H903"/>
+  <dimension ref="A1:H925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25729,6 +25729,622 @@
         <v>0</v>
       </c>
       <c r="H903" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>0</v>
+      </c>
+      <c r="D904" t="n">
+        <v>0</v>
+      </c>
+      <c r="E904" t="n">
+        <v>0</v>
+      </c>
+      <c r="F904" t="n">
+        <v>0</v>
+      </c>
+      <c r="G904" t="n">
+        <v>0</v>
+      </c>
+      <c r="H904" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>0</v>
+      </c>
+      <c r="D905" t="n">
+        <v>0</v>
+      </c>
+      <c r="E905" t="n">
+        <v>0</v>
+      </c>
+      <c r="F905" t="n">
+        <v>0</v>
+      </c>
+      <c r="G905" t="n">
+        <v>0</v>
+      </c>
+      <c r="H905" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D906" t="n">
+        <v>0</v>
+      </c>
+      <c r="E906" t="n">
+        <v>0</v>
+      </c>
+      <c r="F906" t="n">
+        <v>0</v>
+      </c>
+      <c r="G906" t="n">
+        <v>0</v>
+      </c>
+      <c r="H906" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>85632.512</v>
+      </c>
+      <c r="D907" t="n">
+        <v>0</v>
+      </c>
+      <c r="E907" t="n">
+        <v>2079.184</v>
+      </c>
+      <c r="F907" t="n">
+        <v>-2079.184</v>
+      </c>
+      <c r="G907" t="n">
+        <v>0</v>
+      </c>
+      <c r="H907" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D908" t="n">
+        <v>0</v>
+      </c>
+      <c r="E908" t="n">
+        <v>0</v>
+      </c>
+      <c r="F908" t="n">
+        <v>0</v>
+      </c>
+      <c r="G908" t="n">
+        <v>0</v>
+      </c>
+      <c r="H908" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>0</v>
+      </c>
+      <c r="D909" t="n">
+        <v>0</v>
+      </c>
+      <c r="E909" t="n">
+        <v>0</v>
+      </c>
+      <c r="F909" t="n">
+        <v>0</v>
+      </c>
+      <c r="G909" t="n">
+        <v>0</v>
+      </c>
+      <c r="H909" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D910" t="n">
+        <v>0</v>
+      </c>
+      <c r="E910" t="n">
+        <v>0</v>
+      </c>
+      <c r="F910" t="n">
+        <v>0</v>
+      </c>
+      <c r="G910" t="n">
+        <v>0</v>
+      </c>
+      <c r="H910" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D911" t="n">
+        <v>0</v>
+      </c>
+      <c r="E911" t="n">
+        <v>0</v>
+      </c>
+      <c r="F911" t="n">
+        <v>0</v>
+      </c>
+      <c r="G911" t="n">
+        <v>0</v>
+      </c>
+      <c r="H911" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D912" t="n">
+        <v>0</v>
+      </c>
+      <c r="E912" t="n">
+        <v>0</v>
+      </c>
+      <c r="F912" t="n">
+        <v>0</v>
+      </c>
+      <c r="G912" t="n">
+        <v>0</v>
+      </c>
+      <c r="H912" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D913" t="n">
+        <v>0</v>
+      </c>
+      <c r="E913" t="n">
+        <v>0</v>
+      </c>
+      <c r="F913" t="n">
+        <v>0</v>
+      </c>
+      <c r="G913" t="n">
+        <v>0</v>
+      </c>
+      <c r="H913" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D914" t="n">
+        <v>0</v>
+      </c>
+      <c r="E914" t="n">
+        <v>0</v>
+      </c>
+      <c r="F914" t="n">
+        <v>0</v>
+      </c>
+      <c r="G914" t="n">
+        <v>0</v>
+      </c>
+      <c r="H914" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>0</v>
+      </c>
+      <c r="D915" t="n">
+        <v>0</v>
+      </c>
+      <c r="E915" t="n">
+        <v>0</v>
+      </c>
+      <c r="F915" t="n">
+        <v>0</v>
+      </c>
+      <c r="G915" t="n">
+        <v>0</v>
+      </c>
+      <c r="H915" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D916" t="n">
+        <v>0</v>
+      </c>
+      <c r="E916" t="n">
+        <v>0</v>
+      </c>
+      <c r="F916" t="n">
+        <v>0</v>
+      </c>
+      <c r="G916" t="n">
+        <v>0</v>
+      </c>
+      <c r="H916" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D917" t="n">
+        <v>0</v>
+      </c>
+      <c r="E917" t="n">
+        <v>0</v>
+      </c>
+      <c r="F917" t="n">
+        <v>0</v>
+      </c>
+      <c r="G917" t="n">
+        <v>0</v>
+      </c>
+      <c r="H917" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D918" t="n">
+        <v>0</v>
+      </c>
+      <c r="E918" t="n">
+        <v>0</v>
+      </c>
+      <c r="F918" t="n">
+        <v>0</v>
+      </c>
+      <c r="G918" t="n">
+        <v>0</v>
+      </c>
+      <c r="H918" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>81283.64999999999</v>
+      </c>
+      <c r="D919" t="n">
+        <v>0</v>
+      </c>
+      <c r="E919" t="n">
+        <v>0</v>
+      </c>
+      <c r="F919" t="n">
+        <v>0</v>
+      </c>
+      <c r="G919" t="n">
+        <v>0</v>
+      </c>
+      <c r="H919" t="n">
+        <v>81283.64999999999</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D920" t="n">
+        <v>0</v>
+      </c>
+      <c r="E920" t="n">
+        <v>0</v>
+      </c>
+      <c r="F920" t="n">
+        <v>0</v>
+      </c>
+      <c r="G920" t="n">
+        <v>0</v>
+      </c>
+      <c r="H920" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>0</v>
+      </c>
+      <c r="D921" t="n">
+        <v>0</v>
+      </c>
+      <c r="E921" t="n">
+        <v>0</v>
+      </c>
+      <c r="F921" t="n">
+        <v>0</v>
+      </c>
+      <c r="G921" t="n">
+        <v>0</v>
+      </c>
+      <c r="H921" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D922" t="n">
+        <v>0</v>
+      </c>
+      <c r="E922" t="n">
+        <v>0</v>
+      </c>
+      <c r="F922" t="n">
+        <v>0</v>
+      </c>
+      <c r="G922" t="n">
+        <v>0</v>
+      </c>
+      <c r="H922" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D923" t="n">
+        <v>0</v>
+      </c>
+      <c r="E923" t="n">
+        <v>0</v>
+      </c>
+      <c r="F923" t="n">
+        <v>0</v>
+      </c>
+      <c r="G923" t="n">
+        <v>0</v>
+      </c>
+      <c r="H923" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D924" t="n">
+        <v>0</v>
+      </c>
+      <c r="E924" t="n">
+        <v>0</v>
+      </c>
+      <c r="F924" t="n">
+        <v>0</v>
+      </c>
+      <c r="G924" t="n">
+        <v>0</v>
+      </c>
+      <c r="H924" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D925" t="n">
+        <v>0</v>
+      </c>
+      <c r="E925" t="n">
+        <v>0</v>
+      </c>
+      <c r="F925" t="n">
+        <v>0</v>
+      </c>
+      <c r="G925" t="n">
+        <v>0</v>
+      </c>
+      <c r="H925" t="n">
         <v>16.075</v>
       </c>
     </row>
@@ -25791,13 +26407,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85632.512</v>
+        <v>83553.32799999999</v>
       </c>
       <c r="C3" t="n">
         <v>71275.599</v>
       </c>
       <c r="D3" t="n">
-        <v>156908.111</v>
+        <v>154828.927</v>
       </c>
     </row>
     <row r="4">
@@ -25987,13 +26603,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>271962.994</v>
+        <v>269883.81</v>
       </c>
       <c r="C2" t="n">
         <v>313567.939</v>
       </c>
       <c r="D2" t="n">
-        <v>585530.933</v>
+        <v>583451.7490000001</v>
       </c>
     </row>
     <row r="3">
@@ -26119,10 +26735,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2079.184</v>
       </c>
       <c r="E11" t="n">
-        <v>85632.512</v>
+        <v>83553.32799999999</v>
       </c>
     </row>
     <row r="12">

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H925"/>
+  <dimension ref="A1:H947"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26345,6 +26345,622 @@
         <v>0</v>
       </c>
       <c r="H925" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>0</v>
+      </c>
+      <c r="D926" t="n">
+        <v>0</v>
+      </c>
+      <c r="E926" t="n">
+        <v>0</v>
+      </c>
+      <c r="F926" t="n">
+        <v>0</v>
+      </c>
+      <c r="G926" t="n">
+        <v>0</v>
+      </c>
+      <c r="H926" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>0</v>
+      </c>
+      <c r="D927" t="n">
+        <v>0</v>
+      </c>
+      <c r="E927" t="n">
+        <v>0</v>
+      </c>
+      <c r="F927" t="n">
+        <v>0</v>
+      </c>
+      <c r="G927" t="n">
+        <v>0</v>
+      </c>
+      <c r="H927" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D928" t="n">
+        <v>0</v>
+      </c>
+      <c r="E928" t="n">
+        <v>0</v>
+      </c>
+      <c r="F928" t="n">
+        <v>0</v>
+      </c>
+      <c r="G928" t="n">
+        <v>0</v>
+      </c>
+      <c r="H928" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D929" t="n">
+        <v>0</v>
+      </c>
+      <c r="E929" t="n">
+        <v>0</v>
+      </c>
+      <c r="F929" t="n">
+        <v>0</v>
+      </c>
+      <c r="G929" t="n">
+        <v>0</v>
+      </c>
+      <c r="H929" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D930" t="n">
+        <v>0</v>
+      </c>
+      <c r="E930" t="n">
+        <v>0</v>
+      </c>
+      <c r="F930" t="n">
+        <v>0</v>
+      </c>
+      <c r="G930" t="n">
+        <v>0</v>
+      </c>
+      <c r="H930" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>0</v>
+      </c>
+      <c r="D931" t="n">
+        <v>0</v>
+      </c>
+      <c r="E931" t="n">
+        <v>0</v>
+      </c>
+      <c r="F931" t="n">
+        <v>0</v>
+      </c>
+      <c r="G931" t="n">
+        <v>0</v>
+      </c>
+      <c r="H931" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D932" t="n">
+        <v>0</v>
+      </c>
+      <c r="E932" t="n">
+        <v>0</v>
+      </c>
+      <c r="F932" t="n">
+        <v>0</v>
+      </c>
+      <c r="G932" t="n">
+        <v>0</v>
+      </c>
+      <c r="H932" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D933" t="n">
+        <v>0</v>
+      </c>
+      <c r="E933" t="n">
+        <v>0</v>
+      </c>
+      <c r="F933" t="n">
+        <v>0</v>
+      </c>
+      <c r="G933" t="n">
+        <v>0</v>
+      </c>
+      <c r="H933" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D934" t="n">
+        <v>0</v>
+      </c>
+      <c r="E934" t="n">
+        <v>0</v>
+      </c>
+      <c r="F934" t="n">
+        <v>0</v>
+      </c>
+      <c r="G934" t="n">
+        <v>0</v>
+      </c>
+      <c r="H934" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D935" t="n">
+        <v>0</v>
+      </c>
+      <c r="E935" t="n">
+        <v>0</v>
+      </c>
+      <c r="F935" t="n">
+        <v>0</v>
+      </c>
+      <c r="G935" t="n">
+        <v>0</v>
+      </c>
+      <c r="H935" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D936" t="n">
+        <v>0</v>
+      </c>
+      <c r="E936" t="n">
+        <v>0</v>
+      </c>
+      <c r="F936" t="n">
+        <v>0</v>
+      </c>
+      <c r="G936" t="n">
+        <v>0</v>
+      </c>
+      <c r="H936" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>0</v>
+      </c>
+      <c r="D937" t="n">
+        <v>0</v>
+      </c>
+      <c r="E937" t="n">
+        <v>0</v>
+      </c>
+      <c r="F937" t="n">
+        <v>0</v>
+      </c>
+      <c r="G937" t="n">
+        <v>0</v>
+      </c>
+      <c r="H937" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D938" t="n">
+        <v>0</v>
+      </c>
+      <c r="E938" t="n">
+        <v>0</v>
+      </c>
+      <c r="F938" t="n">
+        <v>0</v>
+      </c>
+      <c r="G938" t="n">
+        <v>0</v>
+      </c>
+      <c r="H938" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D939" t="n">
+        <v>0</v>
+      </c>
+      <c r="E939" t="n">
+        <v>0</v>
+      </c>
+      <c r="F939" t="n">
+        <v>0</v>
+      </c>
+      <c r="G939" t="n">
+        <v>0</v>
+      </c>
+      <c r="H939" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D940" t="n">
+        <v>0</v>
+      </c>
+      <c r="E940" t="n">
+        <v>0</v>
+      </c>
+      <c r="F940" t="n">
+        <v>0</v>
+      </c>
+      <c r="G940" t="n">
+        <v>0</v>
+      </c>
+      <c r="H940" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>81283.64999999999</v>
+      </c>
+      <c r="D941" t="n">
+        <v>0</v>
+      </c>
+      <c r="E941" t="n">
+        <v>1010.96</v>
+      </c>
+      <c r="F941" t="n">
+        <v>-1010.96</v>
+      </c>
+      <c r="G941" t="n">
+        <v>0</v>
+      </c>
+      <c r="H941" t="n">
+        <v>80272.69</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D942" t="n">
+        <v>0</v>
+      </c>
+      <c r="E942" t="n">
+        <v>0</v>
+      </c>
+      <c r="F942" t="n">
+        <v>0</v>
+      </c>
+      <c r="G942" t="n">
+        <v>0</v>
+      </c>
+      <c r="H942" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>0</v>
+      </c>
+      <c r="D943" t="n">
+        <v>0</v>
+      </c>
+      <c r="E943" t="n">
+        <v>0</v>
+      </c>
+      <c r="F943" t="n">
+        <v>0</v>
+      </c>
+      <c r="G943" t="n">
+        <v>0</v>
+      </c>
+      <c r="H943" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D944" t="n">
+        <v>0</v>
+      </c>
+      <c r="E944" t="n">
+        <v>0</v>
+      </c>
+      <c r="F944" t="n">
+        <v>0</v>
+      </c>
+      <c r="G944" t="n">
+        <v>0</v>
+      </c>
+      <c r="H944" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D945" t="n">
+        <v>0</v>
+      </c>
+      <c r="E945" t="n">
+        <v>0</v>
+      </c>
+      <c r="F945" t="n">
+        <v>0</v>
+      </c>
+      <c r="G945" t="n">
+        <v>0</v>
+      </c>
+      <c r="H945" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D946" t="n">
+        <v>0</v>
+      </c>
+      <c r="E946" t="n">
+        <v>0</v>
+      </c>
+      <c r="F946" t="n">
+        <v>0</v>
+      </c>
+      <c r="G946" t="n">
+        <v>0</v>
+      </c>
+      <c r="H946" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D947" t="n">
+        <v>0</v>
+      </c>
+      <c r="E947" t="n">
+        <v>0</v>
+      </c>
+      <c r="F947" t="n">
+        <v>0</v>
+      </c>
+      <c r="G947" t="n">
+        <v>0</v>
+      </c>
+      <c r="H947" t="n">
         <v>16.075</v>
       </c>
     </row>
@@ -26503,13 +27119,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81283.64999999999</v>
+        <v>80272.69</v>
       </c>
       <c r="C9" t="n">
         <v>59209.788</v>
       </c>
       <c r="D9" t="n">
-        <v>140493.438</v>
+        <v>139482.478</v>
       </c>
     </row>
     <row r="10">
@@ -26603,13 +27219,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>269883.81</v>
+        <v>268872.85</v>
       </c>
       <c r="C2" t="n">
         <v>313567.939</v>
       </c>
       <c r="D2" t="n">
-        <v>583451.7490000001</v>
+        <v>582440.789</v>
       </c>
     </row>
     <row r="3">
@@ -26987,10 +27603,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1010.96</v>
       </c>
       <c r="E23" t="n">
-        <v>81283.64999999999</v>
+        <v>80272.69</v>
       </c>
     </row>
     <row r="24">

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H947"/>
+  <dimension ref="A1:H969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26961,6 +26961,622 @@
         <v>0</v>
       </c>
       <c r="H947" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C948" t="n">
+        <v>0</v>
+      </c>
+      <c r="D948" t="n">
+        <v>0</v>
+      </c>
+      <c r="E948" t="n">
+        <v>0</v>
+      </c>
+      <c r="F948" t="n">
+        <v>0</v>
+      </c>
+      <c r="G948" t="n">
+        <v>0</v>
+      </c>
+      <c r="H948" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>0</v>
+      </c>
+      <c r="D949" t="n">
+        <v>0</v>
+      </c>
+      <c r="E949" t="n">
+        <v>0</v>
+      </c>
+      <c r="F949" t="n">
+        <v>0</v>
+      </c>
+      <c r="G949" t="n">
+        <v>0</v>
+      </c>
+      <c r="H949" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D950" t="n">
+        <v>0</v>
+      </c>
+      <c r="E950" t="n">
+        <v>0</v>
+      </c>
+      <c r="F950" t="n">
+        <v>0</v>
+      </c>
+      <c r="G950" t="n">
+        <v>0</v>
+      </c>
+      <c r="H950" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D951" t="n">
+        <v>0</v>
+      </c>
+      <c r="E951" t="n">
+        <v>0</v>
+      </c>
+      <c r="F951" t="n">
+        <v>0</v>
+      </c>
+      <c r="G951" t="n">
+        <v>0</v>
+      </c>
+      <c r="H951" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D952" t="n">
+        <v>0</v>
+      </c>
+      <c r="E952" t="n">
+        <v>0</v>
+      </c>
+      <c r="F952" t="n">
+        <v>0</v>
+      </c>
+      <c r="G952" t="n">
+        <v>0</v>
+      </c>
+      <c r="H952" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>0</v>
+      </c>
+      <c r="D953" t="n">
+        <v>0</v>
+      </c>
+      <c r="E953" t="n">
+        <v>0</v>
+      </c>
+      <c r="F953" t="n">
+        <v>0</v>
+      </c>
+      <c r="G953" t="n">
+        <v>0</v>
+      </c>
+      <c r="H953" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D954" t="n">
+        <v>0</v>
+      </c>
+      <c r="E954" t="n">
+        <v>0</v>
+      </c>
+      <c r="F954" t="n">
+        <v>0</v>
+      </c>
+      <c r="G954" t="n">
+        <v>0</v>
+      </c>
+      <c r="H954" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C955" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D955" t="n">
+        <v>0</v>
+      </c>
+      <c r="E955" t="n">
+        <v>0</v>
+      </c>
+      <c r="F955" t="n">
+        <v>0</v>
+      </c>
+      <c r="G955" t="n">
+        <v>0</v>
+      </c>
+      <c r="H955" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C956" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D956" t="n">
+        <v>0</v>
+      </c>
+      <c r="E956" t="n">
+        <v>0</v>
+      </c>
+      <c r="F956" t="n">
+        <v>0</v>
+      </c>
+      <c r="G956" t="n">
+        <v>0</v>
+      </c>
+      <c r="H956" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C957" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D957" t="n">
+        <v>0</v>
+      </c>
+      <c r="E957" t="n">
+        <v>0</v>
+      </c>
+      <c r="F957" t="n">
+        <v>0</v>
+      </c>
+      <c r="G957" t="n">
+        <v>0</v>
+      </c>
+      <c r="H957" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C958" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D958" t="n">
+        <v>0</v>
+      </c>
+      <c r="E958" t="n">
+        <v>0</v>
+      </c>
+      <c r="F958" t="n">
+        <v>0</v>
+      </c>
+      <c r="G958" t="n">
+        <v>0</v>
+      </c>
+      <c r="H958" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>0</v>
+      </c>
+      <c r="D959" t="n">
+        <v>0</v>
+      </c>
+      <c r="E959" t="n">
+        <v>0</v>
+      </c>
+      <c r="F959" t="n">
+        <v>0</v>
+      </c>
+      <c r="G959" t="n">
+        <v>0</v>
+      </c>
+      <c r="H959" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D960" t="n">
+        <v>0</v>
+      </c>
+      <c r="E960" t="n">
+        <v>0</v>
+      </c>
+      <c r="F960" t="n">
+        <v>0</v>
+      </c>
+      <c r="G960" t="n">
+        <v>0</v>
+      </c>
+      <c r="H960" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D961" t="n">
+        <v>0</v>
+      </c>
+      <c r="E961" t="n">
+        <v>0</v>
+      </c>
+      <c r="F961" t="n">
+        <v>0</v>
+      </c>
+      <c r="G961" t="n">
+        <v>0</v>
+      </c>
+      <c r="H961" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D962" t="n">
+        <v>0</v>
+      </c>
+      <c r="E962" t="n">
+        <v>0</v>
+      </c>
+      <c r="F962" t="n">
+        <v>0</v>
+      </c>
+      <c r="G962" t="n">
+        <v>0</v>
+      </c>
+      <c r="H962" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>80272.69</v>
+      </c>
+      <c r="D963" t="n">
+        <v>0</v>
+      </c>
+      <c r="E963" t="n">
+        <v>0</v>
+      </c>
+      <c r="F963" t="n">
+        <v>0</v>
+      </c>
+      <c r="G963" t="n">
+        <v>0</v>
+      </c>
+      <c r="H963" t="n">
+        <v>80272.69</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D964" t="n">
+        <v>0</v>
+      </c>
+      <c r="E964" t="n">
+        <v>0</v>
+      </c>
+      <c r="F964" t="n">
+        <v>0</v>
+      </c>
+      <c r="G964" t="n">
+        <v>0</v>
+      </c>
+      <c r="H964" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>0</v>
+      </c>
+      <c r="D965" t="n">
+        <v>0</v>
+      </c>
+      <c r="E965" t="n">
+        <v>0</v>
+      </c>
+      <c r="F965" t="n">
+        <v>0</v>
+      </c>
+      <c r="G965" t="n">
+        <v>0</v>
+      </c>
+      <c r="H965" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D966" t="n">
+        <v>0</v>
+      </c>
+      <c r="E966" t="n">
+        <v>0</v>
+      </c>
+      <c r="F966" t="n">
+        <v>0</v>
+      </c>
+      <c r="G966" t="n">
+        <v>0</v>
+      </c>
+      <c r="H966" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D967" t="n">
+        <v>0</v>
+      </c>
+      <c r="E967" t="n">
+        <v>0</v>
+      </c>
+      <c r="F967" t="n">
+        <v>0</v>
+      </c>
+      <c r="G967" t="n">
+        <v>0</v>
+      </c>
+      <c r="H967" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D968" t="n">
+        <v>0</v>
+      </c>
+      <c r="E968" t="n">
+        <v>0</v>
+      </c>
+      <c r="F968" t="n">
+        <v>0</v>
+      </c>
+      <c r="G968" t="n">
+        <v>0</v>
+      </c>
+      <c r="H968" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D969" t="n">
+        <v>0</v>
+      </c>
+      <c r="E969" t="n">
+        <v>0</v>
+      </c>
+      <c r="F969" t="n">
+        <v>0</v>
+      </c>
+      <c r="G969" t="n">
+        <v>0</v>
+      </c>
+      <c r="H969" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H969"/>
+  <dimension ref="A1:H991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27577,6 +27577,622 @@
         <v>0</v>
       </c>
       <c r="H969" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>0</v>
+      </c>
+      <c r="D970" t="n">
+        <v>0</v>
+      </c>
+      <c r="E970" t="n">
+        <v>0</v>
+      </c>
+      <c r="F970" t="n">
+        <v>0</v>
+      </c>
+      <c r="G970" t="n">
+        <v>0</v>
+      </c>
+      <c r="H970" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>0</v>
+      </c>
+      <c r="D971" t="n">
+        <v>0</v>
+      </c>
+      <c r="E971" t="n">
+        <v>0</v>
+      </c>
+      <c r="F971" t="n">
+        <v>0</v>
+      </c>
+      <c r="G971" t="n">
+        <v>0</v>
+      </c>
+      <c r="H971" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C972" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D972" t="n">
+        <v>0</v>
+      </c>
+      <c r="E972" t="n">
+        <v>0</v>
+      </c>
+      <c r="F972" t="n">
+        <v>0</v>
+      </c>
+      <c r="G972" t="n">
+        <v>0</v>
+      </c>
+      <c r="H972" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D973" t="n">
+        <v>0</v>
+      </c>
+      <c r="E973" t="n">
+        <v>0</v>
+      </c>
+      <c r="F973" t="n">
+        <v>0</v>
+      </c>
+      <c r="G973" t="n">
+        <v>0</v>
+      </c>
+      <c r="H973" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D974" t="n">
+        <v>0</v>
+      </c>
+      <c r="E974" t="n">
+        <v>0</v>
+      </c>
+      <c r="F974" t="n">
+        <v>0</v>
+      </c>
+      <c r="G974" t="n">
+        <v>0</v>
+      </c>
+      <c r="H974" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>0</v>
+      </c>
+      <c r="D975" t="n">
+        <v>0</v>
+      </c>
+      <c r="E975" t="n">
+        <v>0</v>
+      </c>
+      <c r="F975" t="n">
+        <v>0</v>
+      </c>
+      <c r="G975" t="n">
+        <v>0</v>
+      </c>
+      <c r="H975" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D976" t="n">
+        <v>0</v>
+      </c>
+      <c r="E976" t="n">
+        <v>0</v>
+      </c>
+      <c r="F976" t="n">
+        <v>0</v>
+      </c>
+      <c r="G976" t="n">
+        <v>0</v>
+      </c>
+      <c r="H976" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D977" t="n">
+        <v>0</v>
+      </c>
+      <c r="E977" t="n">
+        <v>0</v>
+      </c>
+      <c r="F977" t="n">
+        <v>0</v>
+      </c>
+      <c r="G977" t="n">
+        <v>0</v>
+      </c>
+      <c r="H977" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D978" t="n">
+        <v>0</v>
+      </c>
+      <c r="E978" t="n">
+        <v>0</v>
+      </c>
+      <c r="F978" t="n">
+        <v>0</v>
+      </c>
+      <c r="G978" t="n">
+        <v>0</v>
+      </c>
+      <c r="H978" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D979" t="n">
+        <v>0</v>
+      </c>
+      <c r="E979" t="n">
+        <v>0</v>
+      </c>
+      <c r="F979" t="n">
+        <v>0</v>
+      </c>
+      <c r="G979" t="n">
+        <v>0</v>
+      </c>
+      <c r="H979" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D980" t="n">
+        <v>0</v>
+      </c>
+      <c r="E980" t="n">
+        <v>0</v>
+      </c>
+      <c r="F980" t="n">
+        <v>0</v>
+      </c>
+      <c r="G980" t="n">
+        <v>0</v>
+      </c>
+      <c r="H980" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>0</v>
+      </c>
+      <c r="D981" t="n">
+        <v>0</v>
+      </c>
+      <c r="E981" t="n">
+        <v>0</v>
+      </c>
+      <c r="F981" t="n">
+        <v>0</v>
+      </c>
+      <c r="G981" t="n">
+        <v>0</v>
+      </c>
+      <c r="H981" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D982" t="n">
+        <v>0</v>
+      </c>
+      <c r="E982" t="n">
+        <v>0</v>
+      </c>
+      <c r="F982" t="n">
+        <v>0</v>
+      </c>
+      <c r="G982" t="n">
+        <v>0</v>
+      </c>
+      <c r="H982" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C983" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D983" t="n">
+        <v>0</v>
+      </c>
+      <c r="E983" t="n">
+        <v>0</v>
+      </c>
+      <c r="F983" t="n">
+        <v>0</v>
+      </c>
+      <c r="G983" t="n">
+        <v>0</v>
+      </c>
+      <c r="H983" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C984" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D984" t="n">
+        <v>0</v>
+      </c>
+      <c r="E984" t="n">
+        <v>0</v>
+      </c>
+      <c r="F984" t="n">
+        <v>0</v>
+      </c>
+      <c r="G984" t="n">
+        <v>0</v>
+      </c>
+      <c r="H984" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C985" t="n">
+        <v>80272.69</v>
+      </c>
+      <c r="D985" t="n">
+        <v>0</v>
+      </c>
+      <c r="E985" t="n">
+        <v>0</v>
+      </c>
+      <c r="F985" t="n">
+        <v>0</v>
+      </c>
+      <c r="G985" t="n">
+        <v>0</v>
+      </c>
+      <c r="H985" t="n">
+        <v>80272.69</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C986" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D986" t="n">
+        <v>0</v>
+      </c>
+      <c r="E986" t="n">
+        <v>0</v>
+      </c>
+      <c r="F986" t="n">
+        <v>0</v>
+      </c>
+      <c r="G986" t="n">
+        <v>0</v>
+      </c>
+      <c r="H986" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C987" t="n">
+        <v>0</v>
+      </c>
+      <c r="D987" t="n">
+        <v>0</v>
+      </c>
+      <c r="E987" t="n">
+        <v>0</v>
+      </c>
+      <c r="F987" t="n">
+        <v>0</v>
+      </c>
+      <c r="G987" t="n">
+        <v>0</v>
+      </c>
+      <c r="H987" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C988" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D988" t="n">
+        <v>0</v>
+      </c>
+      <c r="E988" t="n">
+        <v>0</v>
+      </c>
+      <c r="F988" t="n">
+        <v>0</v>
+      </c>
+      <c r="G988" t="n">
+        <v>0</v>
+      </c>
+      <c r="H988" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C989" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D989" t="n">
+        <v>0</v>
+      </c>
+      <c r="E989" t="n">
+        <v>0</v>
+      </c>
+      <c r="F989" t="n">
+        <v>0</v>
+      </c>
+      <c r="G989" t="n">
+        <v>0</v>
+      </c>
+      <c r="H989" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C990" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D990" t="n">
+        <v>0</v>
+      </c>
+      <c r="E990" t="n">
+        <v>0</v>
+      </c>
+      <c r="F990" t="n">
+        <v>0</v>
+      </c>
+      <c r="G990" t="n">
+        <v>0</v>
+      </c>
+      <c r="H990" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C991" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D991" t="n">
+        <v>0</v>
+      </c>
+      <c r="E991" t="n">
+        <v>0</v>
+      </c>
+      <c r="F991" t="n">
+        <v>0</v>
+      </c>
+      <c r="G991" t="n">
+        <v>0</v>
+      </c>
+      <c r="H991" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H991"/>
+  <dimension ref="A1:H1013"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28193,6 +28193,622 @@
         <v>0</v>
       </c>
       <c r="H991" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C992" t="n">
+        <v>0</v>
+      </c>
+      <c r="D992" t="n">
+        <v>0</v>
+      </c>
+      <c r="E992" t="n">
+        <v>0</v>
+      </c>
+      <c r="F992" t="n">
+        <v>0</v>
+      </c>
+      <c r="G992" t="n">
+        <v>0</v>
+      </c>
+      <c r="H992" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C993" t="n">
+        <v>0</v>
+      </c>
+      <c r="D993" t="n">
+        <v>0</v>
+      </c>
+      <c r="E993" t="n">
+        <v>0</v>
+      </c>
+      <c r="F993" t="n">
+        <v>0</v>
+      </c>
+      <c r="G993" t="n">
+        <v>0</v>
+      </c>
+      <c r="H993" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C994" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D994" t="n">
+        <v>0</v>
+      </c>
+      <c r="E994" t="n">
+        <v>0</v>
+      </c>
+      <c r="F994" t="n">
+        <v>0</v>
+      </c>
+      <c r="G994" t="n">
+        <v>0</v>
+      </c>
+      <c r="H994" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C995" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D995" t="n">
+        <v>0</v>
+      </c>
+      <c r="E995" t="n">
+        <v>0</v>
+      </c>
+      <c r="F995" t="n">
+        <v>0</v>
+      </c>
+      <c r="G995" t="n">
+        <v>0</v>
+      </c>
+      <c r="H995" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C996" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D996" t="n">
+        <v>0</v>
+      </c>
+      <c r="E996" t="n">
+        <v>0</v>
+      </c>
+      <c r="F996" t="n">
+        <v>0</v>
+      </c>
+      <c r="G996" t="n">
+        <v>0</v>
+      </c>
+      <c r="H996" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C997" t="n">
+        <v>0</v>
+      </c>
+      <c r="D997" t="n">
+        <v>0</v>
+      </c>
+      <c r="E997" t="n">
+        <v>0</v>
+      </c>
+      <c r="F997" t="n">
+        <v>0</v>
+      </c>
+      <c r="G997" t="n">
+        <v>0</v>
+      </c>
+      <c r="H997" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C998" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D998" t="n">
+        <v>0</v>
+      </c>
+      <c r="E998" t="n">
+        <v>0</v>
+      </c>
+      <c r="F998" t="n">
+        <v>0</v>
+      </c>
+      <c r="G998" t="n">
+        <v>0</v>
+      </c>
+      <c r="H998" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C999" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E999" t="n">
+        <v>0</v>
+      </c>
+      <c r="F999" t="n">
+        <v>0</v>
+      </c>
+      <c r="G999" t="n">
+        <v>0</v>
+      </c>
+      <c r="H999" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C1000" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1000" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C1002" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1002" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1003" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C1005" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1005" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1006" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1006" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1007" t="n">
+        <v>80272.69</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1007" t="n">
+        <v>80272.69</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1008" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1008" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1010" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1011" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1012" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1013" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1013" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1013"/>
+  <dimension ref="A1:H1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28809,6 +28809,622 @@
         <v>0</v>
       </c>
       <c r="H1013" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1016" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C1021" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C1022" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C1023" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C1024" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>80272.69</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>80272.69</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1033" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1034" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1035" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1035" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1035"/>
+  <dimension ref="A1:H1057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29425,6 +29425,622 @@
         <v>0</v>
       </c>
       <c r="H1035" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1038" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1039" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1040" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1040" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1041" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1042" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1043" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1044" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C1045" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1045" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1046" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1047" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1048" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C1049" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1049" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1050" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1050" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1051" t="n">
+        <v>80272.69</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1051" t="n">
+        <v>80272.69</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1052" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1052" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1053" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1054" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1054" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1055" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1055" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1056" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1056" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1057" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1057" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1057"/>
+  <dimension ref="A1:H1079"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30041,6 +30041,622 @@
         <v>0</v>
       </c>
       <c r="H1057" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1058" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1059" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1060" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1060" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1061" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1061" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1062" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1062" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1063" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C1064" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C1065" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1065" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C1066" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1066" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C1067" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1067" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C1068" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1068" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C1070" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C1071" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1072" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>80272.69</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>80272.69</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1074" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1074" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1075" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1076" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1076" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1077" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1077" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1078" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1078" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1079" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1079" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1079"/>
+  <dimension ref="A1:H1101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30657,6 +30657,622 @@
         <v>0</v>
       </c>
       <c r="H1079" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1080" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1081" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1082" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1082" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1083" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1083" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1084" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1084" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C1086" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1086" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C1087" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C1088" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C1089" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C1090" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C1092" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C1093" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1094" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1095" t="n">
+        <v>80272.69</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>80272.69</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1096" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1098" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1099" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1099" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1100" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1100" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1101" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1101" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1101"/>
+  <dimension ref="A1:H1123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31273,6 +31273,622 @@
         <v>0</v>
       </c>
       <c r="H1101" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1104" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1104" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1105" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1105" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1106" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1106" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C1108" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1108" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C1109" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1109" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C1110" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1110" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C1111" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1111" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C1112" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1112" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C1114" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1114" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C1115" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1115" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1116" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1116" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1117" t="n">
+        <v>80272.69</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1117" t="n">
+        <v>80272.69</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1118" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1118" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1120" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1120" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1121" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1121" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1122" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1122" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1123" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1123" t="n">
         <v>16.075</v>
       </c>
     </row>

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1123"/>
+  <dimension ref="A1:H1145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31889,6 +31889,622 @@
         <v>0</v>
       </c>
       <c r="H1123" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1126" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1126" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1127" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1127" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1128" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1128" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C1130" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1130" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C1131" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1131" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C1132" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1132" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C1133" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1133" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C1134" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1134" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C1136" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1136" t="n">
+        <v>113601.788</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C1137" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1137" t="n">
+        <v>75484.511</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1138" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1138" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1139" t="n">
+        <v>80272.69</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>3167.151</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>-3167.151</v>
+      </c>
+      <c r="G1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1139" t="n">
+        <v>77105.539</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1140" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1140" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1142" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1142" t="n">
+        <v>48292.647</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1143" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1143" t="n">
+        <v>1804.683</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1144" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1144" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1145" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1145" t="n">
         <v>16.075</v>
       </c>
     </row>
@@ -32047,13 +32663,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80272.69</v>
+        <v>77105.539</v>
       </c>
       <c r="C9" t="n">
         <v>59209.788</v>
       </c>
       <c r="D9" t="n">
-        <v>139482.478</v>
+        <v>136315.327</v>
       </c>
     </row>
     <row r="10">
@@ -32147,13 +32763,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>268872.85</v>
+        <v>265705.699</v>
       </c>
       <c r="C2" t="n">
         <v>313567.939</v>
       </c>
       <c r="D2" t="n">
-        <v>582440.789</v>
+        <v>579273.638</v>
       </c>
     </row>
     <row r="3">
@@ -32531,10 +33147,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1010.96</v>
+        <v>4178.111</v>
       </c>
       <c r="E23" t="n">
-        <v>80272.69</v>
+        <v>77105.539</v>
       </c>
     </row>
     <row r="24">

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1145"/>
+  <dimension ref="A1:H1167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32505,6 +32505,622 @@
         <v>0</v>
       </c>
       <c r="H1145" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1148" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1148" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1149" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1149" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1150" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1150" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C1152" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1152" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C1153" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C1154" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1154" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C1155" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C1156" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C1158" t="n">
+        <v>113601.788</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1158" t="n">
+        <v>-2925.516</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>110676.272</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C1159" t="n">
+        <v>75484.511</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1159" t="n">
+        <v>2925.516</v>
+      </c>
+      <c r="H1159" t="n">
+        <v>78410.027</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1160" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1161" t="n">
+        <v>77105.539</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>77105.539</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1162" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1164" t="n">
+        <v>48292.647</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1164" t="n">
+        <v>-2086.054</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>46206.593</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1165" t="n">
+        <v>1804.683</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1165" t="n">
+        <v>2086.054</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>3890.737</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1166" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1166" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1167" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1167" t="n">
         <v>16.075</v>
       </c>
     </row>
@@ -32647,10 +33263,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75484.511</v>
+        <v>78410.027</v>
       </c>
       <c r="C8" t="n">
-        <v>113601.788</v>
+        <v>110676.272</v>
       </c>
       <c r="D8" t="n">
         <v>189086.299</v>
@@ -32695,13 +33311,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1804.683</v>
+        <v>3890.737</v>
       </c>
       <c r="C11" t="n">
-        <v>48292.647</v>
+        <v>46206.593</v>
       </c>
       <c r="D11" t="n">
-        <v>50097.32999999999</v>
+        <v>50097.33</v>
       </c>
     </row>
     <row r="12">
@@ -32763,10 +33379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>265705.699</v>
+        <v>270717.269</v>
       </c>
       <c r="C2" t="n">
-        <v>313567.939</v>
+        <v>308556.369</v>
       </c>
       <c r="D2" t="n">
         <v>579273.638</v>
@@ -33108,7 +33724,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>75484.511</v>
+        <v>78410.027</v>
       </c>
     </row>
     <row r="22">
@@ -33129,7 +33745,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>113601.788</v>
+        <v>110676.272</v>
       </c>
     </row>
     <row r="23">
@@ -33234,7 +33850,7 @@
         <v>1627.601</v>
       </c>
       <c r="E27" t="n">
-        <v>1804.683</v>
+        <v>3890.737</v>
       </c>
     </row>
     <row r="28">
@@ -33255,7 +33871,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>48292.647</v>
+        <v>46206.593</v>
       </c>
     </row>
     <row r="29">

--- a/platinum_daily_report.xlsx
+++ b/platinum_daily_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1167"/>
+  <dimension ref="A1:H1189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33121,6 +33121,622 @@
         <v>0</v>
       </c>
       <c r="H1167" t="n">
+        <v>16.075</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>ASAHI DEPOSITORY LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1170" t="n">
+        <v>71275.599</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1170" t="n">
+        <v>71275.599</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>BRINK'S, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1171" t="n">
+        <v>83553.32799999999</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1171" t="n">
+        <v>83553.32799999999</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Registered</t>
+        </is>
+      </c>
+      <c r="C1172" t="n">
+        <v>1246.06</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1172" t="n">
+        <v>1246.06</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>CNT DEPOSITORY, INC. Eligible</t>
+        </is>
+      </c>
+      <c r="C1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Registered</t>
+        </is>
+      </c>
+      <c r="C1174" t="n">
+        <v>1633.941</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1174" t="n">
+        <v>1633.941</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>DELAWARE DEPOSITORY Eligible</t>
+        </is>
+      </c>
+      <c r="C1175" t="n">
+        <v>18459.584</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1175" t="n">
+        <v>18459.584</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Registered</t>
+        </is>
+      </c>
+      <c r="C1176" t="n">
+        <v>1394.758</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1176" t="n">
+        <v>1394.758</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>HSBC BANK, USA Eligible</t>
+        </is>
+      </c>
+      <c r="C1177" t="n">
+        <v>9281.978999999999</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>9281.978999999999</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Registered</t>
+        </is>
+      </c>
+      <c r="C1178" t="n">
+        <v>2395.448</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>2395.448</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL DEPOSITORY SERVICES OF DELAWARE Eligible</t>
+        </is>
+      </c>
+      <c r="C1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Registered</t>
+        </is>
+      </c>
+      <c r="C1180" t="n">
+        <v>110676.272</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1180" t="n">
+        <v>110676.272</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>JP MORGAN CHASE BANK NA Eligible</t>
+        </is>
+      </c>
+      <c r="C1181" t="n">
+        <v>78410.027</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1181" t="n">
+        <v>78410.027</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1182" t="n">
+        <v>59209.788</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>59209.788</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>LOOMIS INTERNATIONAL (US) LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1183" t="n">
+        <v>77105.539</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>77105.539</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1184" t="n">
+        <v>395.145</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>395.145</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>MALCA-AMIT USA, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1186" t="n">
+        <v>46206.593</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1186" t="n">
+        <v>46206.593</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>MANFRA, TORDELLA &amp; BROOKES, LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1187" t="n">
+        <v>3890.737</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1187" t="n">
+        <v>3890.737</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Registered</t>
+        </is>
+      </c>
+      <c r="C1188" t="n">
+        <v>14122.765</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1188" t="n">
+        <v>14122.765</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>STONEX PRECIOUS METALS LLC Eligible</t>
+        </is>
+      </c>
+      <c r="C1189" t="n">
+        <v>16.075</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1189" t="n">
         <v>16.075</v>
       </c>
     </row>
